--- a/Data/National Accounts/PSA-Annual-Indicators-Derived.xlsx
+++ b/Data/National Accounts/PSA-Annual-Indicators-Derived.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\Derived indicators\2023-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E606A0-8DDD-4C94-A84E-ABFA900AE8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883E107B-DBDF-472D-9BAC-757E45F4DE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="15675" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Annual" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Annual!$A$1:$Z$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Annual!$A$1:$AA$61</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Annual!$A:$A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -177,28 +177,20 @@
     <t>ANNUAL</t>
   </si>
   <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>Note: * December 2025 interest payment and amortization data are not yet available as of posting.</t>
-  </si>
-  <si>
-    <t>As of January 2026</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="General_)"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,6 +242,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -293,7 +291,7 @@
     <xf numFmtId="40" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="37" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -323,17 +321,25 @@
       <alignment horizontal="left" wrapText="1" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -652,83 +658,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z61"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AA66"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="25" width="12.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="11.42578125" style="1" customWidth="1"/>
-    <col min="27" max="16384" width="8.85546875" style="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="26" width="12.7109375" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B2" s="18"/>
+    </row>
+    <row r="3" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="18"/>
+    </row>
+    <row r="4" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B4" s="18"/>
+    </row>
+    <row r="5" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B5" s="18"/>
+    </row>
+    <row r="6" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B6" s="19"/>
+    </row>
+    <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="25"/>
+      <c r="X7" s="25"/>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="25"/>
+      <c r="AA7" s="25"/>
+    </row>
+    <row r="8" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="13">
+        <v>2000</v>
+      </c>
+      <c r="C8" s="2">
         <v>2001</v>
       </c>
-      <c r="C8" s="2">
+      <c r="D8" s="2">
         <v>2002</v>
       </c>
-      <c r="D8" s="2">
+      <c r="E8" s="2">
         <v>2003</v>
       </c>
-      <c r="E8" s="2">
+      <c r="F8" s="2">
         <v>2004</v>
-      </c>
-      <c r="F8" s="2">
-        <v>2005</v>
       </c>
       <c r="G8" s="2">
         <v>2005</v>
@@ -737,3295 +754,3515 @@
         <v>2005</v>
       </c>
       <c r="I8" s="2">
+        <v>2005</v>
+      </c>
+      <c r="J8" s="2">
         <v>2008</v>
       </c>
-      <c r="J8" s="2">
+      <c r="K8" s="2">
         <v>2009</v>
       </c>
-      <c r="K8" s="2">
+      <c r="L8" s="2">
         <v>2010</v>
       </c>
-      <c r="L8" s="2">
+      <c r="M8" s="2">
         <v>2011</v>
       </c>
-      <c r="M8" s="2">
+      <c r="N8" s="2">
         <v>2012</v>
       </c>
-      <c r="N8" s="2">
+      <c r="O8" s="2">
         <v>2013</v>
       </c>
-      <c r="O8" s="2">
+      <c r="P8" s="2">
         <v>2014</v>
       </c>
-      <c r="P8" s="2">
+      <c r="Q8" s="2">
         <v>2015</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="R8" s="2">
         <v>2016</v>
       </c>
-      <c r="R8" s="14">
+      <c r="S8" s="13">
         <v>2017</v>
       </c>
-      <c r="S8" s="14">
+      <c r="T8" s="13">
         <v>2018</v>
       </c>
-      <c r="T8" s="14">
+      <c r="U8" s="13">
         <v>2019</v>
       </c>
-      <c r="U8" s="14">
+      <c r="V8" s="13">
         <v>2020</v>
       </c>
-      <c r="V8" s="14">
+      <c r="W8" s="13">
         <v>2021</v>
       </c>
-      <c r="W8" s="14">
+      <c r="X8" s="13">
         <v>2022</v>
       </c>
-      <c r="X8" s="14">
+      <c r="Y8" s="13">
         <v>2023</v>
       </c>
-      <c r="Y8" s="14">
+      <c r="Z8" s="13">
         <v>2024</v>
       </c>
-      <c r="Z8" s="14">
+      <c r="AA8" s="13">
         <v>2025</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="7.15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B10" s="19"/>
+    </row>
+    <row r="11" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B11" s="19"/>
+    </row>
+    <row r="12" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B12" s="19"/>
+    </row>
+    <row r="13" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="20">
+        <v>254453.44650388518</v>
+      </c>
+      <c r="C13" s="15">
         <v>246915.30911348455</v>
       </c>
-      <c r="C13" s="18">
+      <c r="D13" s="15">
         <v>248349.87795327106</v>
       </c>
-      <c r="D13" s="18">
+      <c r="E13" s="15">
         <v>256160.29207775265</v>
       </c>
-      <c r="E13" s="18">
+      <c r="F13" s="15">
         <v>264480.1753768638</v>
       </c>
-      <c r="F13" s="18">
+      <c r="G13" s="15">
         <v>271547.93019847199</v>
       </c>
-      <c r="G13" s="18">
+      <c r="H13" s="15">
         <v>280349.32238196861</v>
       </c>
-      <c r="H13" s="18">
+      <c r="I13" s="15">
         <v>293259.02724391967</v>
       </c>
-      <c r="I13" s="18">
+      <c r="J13" s="15">
         <v>301293.80564402189</v>
       </c>
-      <c r="J13" s="18">
+      <c r="K13" s="15">
         <v>297197.63470358466</v>
       </c>
-      <c r="K13" s="18">
+      <c r="L13" s="15">
         <v>310282.17111553409</v>
       </c>
-      <c r="L13" s="18">
+      <c r="M13" s="15">
         <v>312314.556442809</v>
       </c>
-      <c r="M13" s="18">
+      <c r="N13" s="15">
         <v>330034.96223645011</v>
       </c>
-      <c r="N13" s="18">
+      <c r="O13" s="15">
         <v>349570.08618518704</v>
       </c>
-      <c r="O13" s="18">
+      <c r="P13" s="15">
         <v>369208.3616649594</v>
       </c>
-      <c r="P13" s="18">
+      <c r="Q13" s="15">
         <v>382366.6211857961</v>
       </c>
-      <c r="Q13" s="18">
+      <c r="R13" s="15">
         <v>391792.95842696266</v>
       </c>
-      <c r="R13" s="18">
+      <c r="S13" s="15">
         <v>425843.74471370305</v>
       </c>
-      <c r="S13" s="18">
+      <c r="T13" s="15">
         <v>443798.05950892757</v>
       </c>
-      <c r="T13" s="18">
+      <c r="U13" s="15">
         <v>462176.18195137894</v>
       </c>
-      <c r="U13" s="18">
+      <c r="V13" s="15">
         <v>445373.39471345261</v>
       </c>
-      <c r="V13" s="18">
+      <c r="W13" s="15">
         <v>421477.69711930491</v>
       </c>
-      <c r="W13" s="18">
+      <c r="X13" s="15">
         <v>425400.63422567811</v>
       </c>
-      <c r="X13" s="18">
+      <c r="Y13" s="15">
         <v>436782.51145746571</v>
       </c>
-      <c r="Y13" s="18">
-        <v>455396.3328883358</v>
-      </c>
-      <c r="Z13" s="18">
-        <v>454218.95209772373</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z13" s="15">
+        <v>455494.2661500164</v>
+      </c>
+      <c r="AA13" s="15">
+        <v>453565.43526074203</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="20">
+        <v>104511.46398315467</v>
+      </c>
+      <c r="C14" s="15">
         <v>101854.14623403116</v>
       </c>
-      <c r="C14" s="18">
+      <c r="D14" s="15">
         <v>102969.09511974745</v>
       </c>
-      <c r="D14" s="18">
+      <c r="E14" s="15">
         <v>106889.04100800517</v>
       </c>
-      <c r="E14" s="18">
+      <c r="F14" s="15">
         <v>110461.68562841593</v>
       </c>
-      <c r="F14" s="18">
+      <c r="G14" s="15">
         <v>111888.65257717836</v>
       </c>
-      <c r="G14" s="18">
+      <c r="H14" s="15">
         <v>115192.12417677898</v>
       </c>
-      <c r="H14" s="18">
+      <c r="I14" s="15">
         <v>121635.39491874336</v>
       </c>
-      <c r="I14" s="18">
+      <c r="J14" s="15">
         <v>123231.05718245613</v>
       </c>
-      <c r="J14" s="18">
+      <c r="K14" s="15">
         <v>122919.44407391701</v>
       </c>
-      <c r="K14" s="18">
+      <c r="L14" s="15">
         <v>125277.20383499628</v>
       </c>
-      <c r="L14" s="18">
+      <c r="M14" s="15">
         <v>126403.24993019167</v>
       </c>
-      <c r="M14" s="18">
+      <c r="N14" s="15">
         <v>132049.12968488509</v>
       </c>
-      <c r="N14" s="18">
+      <c r="O14" s="15">
         <v>139905.12476582674</v>
       </c>
-      <c r="O14" s="18">
+      <c r="P14" s="15">
         <v>144634.10934885475</v>
       </c>
-      <c r="P14" s="18">
+      <c r="Q14" s="15">
         <v>147769.28735725733</v>
       </c>
-      <c r="Q14" s="18">
+      <c r="R14" s="15">
         <v>151132.57536476798</v>
       </c>
-      <c r="R14" s="18">
+      <c r="S14" s="15">
         <v>169881.73726318689</v>
       </c>
-      <c r="S14" s="18">
+      <c r="T14" s="15">
         <v>176292.5581506266</v>
       </c>
-      <c r="T14" s="18">
+      <c r="U14" s="15">
         <v>191294.20040447154</v>
       </c>
-      <c r="U14" s="18">
+      <c r="V14" s="15">
         <v>182535.21359326085</v>
       </c>
-      <c r="V14" s="18">
+      <c r="W14" s="15">
         <v>166586.43762566624</v>
       </c>
-      <c r="W14" s="18">
+      <c r="X14" s="15">
         <v>164607.27289343343</v>
       </c>
-      <c r="X14" s="18">
+      <c r="Y14" s="15">
         <v>161274.78898220428</v>
       </c>
-      <c r="Y14" s="18">
-        <v>176071.43830514236</v>
-      </c>
-      <c r="Z14" s="18">
-        <v>177103.79864746798</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z14" s="15">
+        <v>176048.13338358526</v>
+      </c>
+      <c r="AA14" s="15">
+        <v>176233.10048141863</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="20">
+        <v>501421.62293625349</v>
+      </c>
+      <c r="C15" s="15">
         <v>480359.28650593956</v>
       </c>
-      <c r="C15" s="18">
+      <c r="D15" s="15">
         <v>502007.44466699823</v>
       </c>
-      <c r="D15" s="18">
+      <c r="E15" s="15">
         <v>509594.57903981645</v>
       </c>
-      <c r="E15" s="18">
+      <c r="F15" s="15">
         <v>514461.3283815899</v>
       </c>
-      <c r="F15" s="18">
+      <c r="G15" s="15">
         <v>537702.86133580504</v>
       </c>
-      <c r="G15" s="18">
+      <c r="H15" s="15">
         <v>559748.02895478182</v>
       </c>
-      <c r="H15" s="18">
+      <c r="I15" s="15">
         <v>574154.27926894277</v>
       </c>
-      <c r="I15" s="18">
+      <c r="J15" s="15">
         <v>614708.80137307663</v>
       </c>
-      <c r="J15" s="18">
+      <c r="K15" s="15">
         <v>600628.2448154334</v>
       </c>
-      <c r="K15" s="18">
+      <c r="L15" s="15">
         <v>622799.27276618558</v>
       </c>
-      <c r="L15" s="18">
+      <c r="M15" s="15">
         <v>616959.81217959942</v>
       </c>
-      <c r="M15" s="18">
+      <c r="N15" s="15">
         <v>637020.73242854595</v>
       </c>
-      <c r="N15" s="18">
+      <c r="O15" s="15">
         <v>663367.43811586639</v>
       </c>
-      <c r="O15" s="18">
+      <c r="P15" s="15">
         <v>695039.20771499758</v>
       </c>
-      <c r="P15" s="18">
+      <c r="Q15" s="15">
         <v>709044.36105244351</v>
       </c>
-      <c r="Q15" s="18">
+      <c r="R15" s="15">
         <v>679006.82884437649</v>
       </c>
-      <c r="R15" s="18">
+      <c r="S15" s="15">
         <v>705909.35345243372</v>
       </c>
-      <c r="S15" s="18">
+      <c r="T15" s="15">
         <v>711492.16364129807</v>
       </c>
-      <c r="T15" s="18">
+      <c r="U15" s="15">
         <v>726384.39463620738</v>
       </c>
-      <c r="U15" s="18">
+      <c r="V15" s="15">
         <v>709838.86444882827</v>
       </c>
-      <c r="V15" s="18">
+      <c r="W15" s="15">
         <v>686024.08554213517</v>
       </c>
-      <c r="W15" s="18">
+      <c r="X15" s="15">
         <v>693463.31517112197</v>
       </c>
-      <c r="X15" s="18">
+      <c r="Y15" s="15">
         <v>726989.53836764488</v>
       </c>
-      <c r="Y15" s="18">
-        <v>726004.88495674066</v>
-      </c>
-      <c r="Z15" s="18">
-        <v>740831.51346674026</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z15" s="15">
+        <v>725934.18432207918</v>
+      </c>
+      <c r="AA15" s="15">
+        <v>743858.16325023433</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="20">
+        <v>287875.59720115783</v>
+      </c>
+      <c r="C16" s="15">
         <v>281792.51902078249</v>
       </c>
-      <c r="C16" s="18">
+      <c r="D16" s="15">
         <v>278566.74242258753</v>
       </c>
-      <c r="D16" s="18">
+      <c r="E16" s="15">
         <v>286835.76595585182</v>
       </c>
-      <c r="E16" s="18">
+      <c r="F16" s="15">
         <v>297519.60066659033</v>
       </c>
-      <c r="F16" s="18">
+      <c r="G16" s="15">
         <v>304718.6752184194</v>
       </c>
-      <c r="G16" s="18">
+      <c r="H16" s="15">
         <v>314555.54714089626</v>
       </c>
-      <c r="H16" s="18">
+      <c r="I16" s="15">
         <v>328339.20274018374</v>
       </c>
-      <c r="I16" s="18">
+      <c r="J16" s="15">
         <v>334239.53322660358</v>
       </c>
-      <c r="J16" s="18">
+      <c r="K16" s="15">
         <v>372962.3778024955</v>
       </c>
-      <c r="K16" s="18">
+      <c r="L16" s="15">
         <v>338644.18944336515</v>
       </c>
-      <c r="L16" s="18">
+      <c r="M16" s="15">
         <v>343036.01678223821</v>
       </c>
-      <c r="M16" s="18">
+      <c r="N16" s="15">
         <v>361721.81090923224</v>
       </c>
-      <c r="N16" s="18">
+      <c r="O16" s="15">
         <v>379660.53608123533</v>
       </c>
-      <c r="O16" s="18">
+      <c r="P16" s="15">
         <v>399643.16263609764</v>
       </c>
-      <c r="P16" s="18">
+      <c r="Q16" s="15">
         <v>410822.00769291929</v>
       </c>
-      <c r="Q16" s="18">
+      <c r="R16" s="15">
         <v>418414.14317879512</v>
       </c>
-      <c r="R16" s="18">
+      <c r="S16" s="15">
         <v>450611.19388242974</v>
       </c>
-      <c r="S16" s="18">
+      <c r="T16" s="15">
         <v>468429.02534502471</v>
       </c>
-      <c r="T16" s="18">
+      <c r="U16" s="15">
         <v>477862.60503334634</v>
       </c>
-      <c r="U16" s="18">
+      <c r="V16" s="15">
         <v>474717.02698616119</v>
       </c>
-      <c r="V16" s="18">
+      <c r="W16" s="15">
         <v>444274.96232086519</v>
       </c>
-      <c r="W16" s="18">
+      <c r="X16" s="15">
         <v>445022.38940026471</v>
       </c>
-      <c r="X16" s="18">
+      <c r="Y16" s="15">
         <v>459103.86478587711</v>
       </c>
-      <c r="Y16" s="18">
-        <v>469073.99679361412</v>
-      </c>
-      <c r="Z16" s="18">
-        <v>463419.84757838334</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z16" s="15">
+        <v>469263.38880246104</v>
+      </c>
+      <c r="AA16" s="15">
+        <v>462546.21936284681</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="16"/>
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
       <c r="I17" s="16"/>
       <c r="J17" s="16"/>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
+      <c r="X17" s="16"/>
+      <c r="Y17" s="16"/>
+      <c r="Z17" s="16"/>
+      <c r="AA17" s="16"/>
+    </row>
+    <row r="18" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="21"/>
+      <c r="C18" s="16">
         <v>-2.9624819368620763</v>
       </c>
-      <c r="C18" s="19">
+      <c r="D18" s="16">
         <v>0.58099631202988178</v>
       </c>
-      <c r="D18" s="19">
+      <c r="E18" s="16">
         <v>3.1449236814004706</v>
       </c>
-      <c r="E18" s="19">
+      <c r="F18" s="16">
         <v>3.2479207575957219</v>
       </c>
-      <c r="F18" s="19">
+      <c r="G18" s="16">
         <v>2.6723193190329511</v>
       </c>
-      <c r="G18" s="19">
+      <c r="H18" s="16">
         <v>3.2411928815159001</v>
       </c>
-      <c r="H18" s="19">
+      <c r="I18" s="16">
         <v>4.6048639434062721</v>
       </c>
-      <c r="I18" s="19">
+      <c r="J18" s="16">
         <v>2.739823041634537</v>
       </c>
-      <c r="J18" s="19">
+      <c r="K18" s="16">
         <v>-1.3595271006921621</v>
       </c>
-      <c r="K18" s="19">
+      <c r="L18" s="16">
         <v>4.4026381384224607</v>
       </c>
-      <c r="L18" s="19">
+      <c r="M18" s="16">
         <v>0.65501195894306363</v>
       </c>
-      <c r="M18" s="19">
+      <c r="N18" s="16">
         <v>5.6738968543357231</v>
       </c>
-      <c r="N18" s="19">
+      <c r="O18" s="16">
         <v>5.9191074231526954</v>
       </c>
-      <c r="O18" s="19">
+      <c r="P18" s="16">
         <v>5.6178363812768595</v>
       </c>
-      <c r="P18" s="19">
+      <c r="Q18" s="16">
         <v>3.5639115705557174</v>
       </c>
-      <c r="Q18" s="19">
+      <c r="R18" s="16">
         <v>2.4652615366722159</v>
       </c>
-      <c r="R18" s="19">
+      <c r="S18" s="16">
         <v>8.6910153830873611</v>
       </c>
-      <c r="S18" s="19">
+      <c r="T18" s="16">
         <v>4.2161743639783396</v>
       </c>
-      <c r="T18" s="19">
+      <c r="U18" s="16">
         <v>4.141100225356368</v>
       </c>
-      <c r="U18" s="19">
+      <c r="V18" s="16">
         <v>-3.6355805197451758</v>
       </c>
-      <c r="V18" s="19">
+      <c r="W18" s="16">
         <v>-5.3653177037038517</v>
       </c>
-      <c r="W18" s="19">
+      <c r="X18" s="16">
         <v>0.93075793409367691</v>
       </c>
-      <c r="X18" s="19">
+      <c r="Y18" s="16">
         <v>2.6755665873665464</v>
       </c>
-      <c r="Y18" s="19">
-        <v>4.261576629695881</v>
-      </c>
-      <c r="Z18" s="19">
-        <v>-0.25853980490896333</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z18" s="16">
+        <v>4.2839981459223111</v>
+      </c>
+      <c r="AA18" s="16">
+        <v>-0.42345887371479307</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="21"/>
+      <c r="C19" s="16">
         <v>-2.5426088659056774</v>
       </c>
-      <c r="C19" s="19">
+      <c r="D19" s="16">
         <v>1.0946524289295638</v>
       </c>
-      <c r="D19" s="19">
+      <c r="E19" s="16">
         <v>3.8069149619107066</v>
       </c>
-      <c r="E19" s="19">
+      <c r="F19" s="16">
         <v>3.3423862602932388</v>
       </c>
-      <c r="F19" s="19">
+      <c r="G19" s="16">
         <v>1.2918207255705312</v>
       </c>
-      <c r="G19" s="19">
+      <c r="H19" s="16">
         <v>2.9524634746333618</v>
       </c>
-      <c r="H19" s="19">
+      <c r="I19" s="16">
         <v>5.5934993716030874</v>
       </c>
-      <c r="I19" s="19">
+      <c r="J19" s="16">
         <v>1.31184041025125</v>
       </c>
-      <c r="J19" s="19">
+      <c r="K19" s="16">
         <v>-0.25286897285783994</v>
       </c>
-      <c r="K19" s="19">
+      <c r="L19" s="16">
         <v>1.9181340908615283</v>
       </c>
-      <c r="L19" s="19">
+      <c r="M19" s="16">
         <v>0.89884357307217044</v>
       </c>
-      <c r="M19" s="19">
+      <c r="N19" s="16">
         <v>4.4665621792251926</v>
       </c>
-      <c r="N19" s="19">
+      <c r="O19" s="16">
         <v>5.9492971287949956</v>
       </c>
-      <c r="O19" s="19">
+      <c r="P19" s="16">
         <v>3.3801367826542332</v>
       </c>
-      <c r="P19" s="19">
+      <c r="Q19" s="16">
         <v>2.167661572029715</v>
       </c>
-      <c r="Q19" s="19">
+      <c r="R19" s="16">
         <v>2.2760399455533218</v>
       </c>
-      <c r="R19" s="19">
+      <c r="S19" s="16">
         <v>12.405771458050424</v>
       </c>
-      <c r="S19" s="19">
+      <c r="T19" s="16">
         <v>3.7736963317650947</v>
       </c>
-      <c r="T19" s="19">
+      <c r="U19" s="16">
         <v>8.5095153256709466</v>
       </c>
-      <c r="U19" s="19">
+      <c r="V19" s="16">
         <v>-4.5788041627455129</v>
       </c>
-      <c r="V19" s="19">
+      <c r="W19" s="16">
         <v>-8.737369438826704</v>
       </c>
-      <c r="W19" s="19">
+      <c r="X19" s="16">
         <v>-1.1880707459992408</v>
       </c>
-      <c r="X19" s="19">
+      <c r="Y19" s="16">
         <v>-2.0245058755007648</v>
       </c>
-      <c r="Y19" s="19">
-        <v>9.1748061903034426</v>
-      </c>
-      <c r="Z19" s="19">
-        <v>0.58633038513404756</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z19" s="16">
+        <v>9.1603557472402741</v>
+      </c>
+      <c r="AA19" s="16">
+        <v>0.10506620790482657</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="21"/>
+      <c r="C20" s="16">
         <v>-4.2005241630737657</v>
       </c>
-      <c r="C20" s="19">
+      <c r="D20" s="16">
         <v>4.5066596543857855</v>
       </c>
-      <c r="D20" s="19">
+      <c r="E20" s="16">
         <v>1.5113589356928969</v>
       </c>
-      <c r="E20" s="19">
+      <c r="F20" s="16">
         <v>0.95502376633271524</v>
       </c>
-      <c r="F20" s="19">
+      <c r="G20" s="16">
         <v>4.5176443149437659</v>
       </c>
-      <c r="G20" s="19">
+      <c r="H20" s="16">
         <v>4.0998791719669043</v>
       </c>
-      <c r="H20" s="19">
+      <c r="I20" s="16">
         <v>2.5737027321135457</v>
       </c>
-      <c r="I20" s="19">
+      <c r="J20" s="16">
         <v>7.0633492718665991</v>
       </c>
-      <c r="J20" s="19">
+      <c r="K20" s="16">
         <v>-2.2906059789922466</v>
       </c>
-      <c r="K20" s="19">
+      <c r="L20" s="16">
         <v>3.6913062517672728</v>
       </c>
-      <c r="L20" s="19">
+      <c r="M20" s="16">
         <v>-0.93761519030842067</v>
       </c>
-      <c r="M20" s="19">
+      <c r="N20" s="16">
         <v>3.2515764970290775</v>
       </c>
-      <c r="N20" s="19">
+      <c r="O20" s="16">
         <v>4.1359259355464815</v>
       </c>
-      <c r="O20" s="19">
+      <c r="P20" s="16">
         <v>4.7743931612150163</v>
       </c>
-      <c r="P20" s="19">
+      <c r="Q20" s="16">
         <v>2.0150163015247813</v>
       </c>
-      <c r="Q20" s="19">
+      <c r="R20" s="16">
         <v>-4.2363403276322344</v>
       </c>
-      <c r="R20" s="19">
+      <c r="S20" s="16">
         <v>3.9620403603073413</v>
       </c>
-      <c r="S20" s="19">
+      <c r="T20" s="16">
         <v>0.79086785882070387</v>
       </c>
-      <c r="T20" s="19">
+      <c r="U20" s="16">
         <v>2.0930983861710217</v>
       </c>
-      <c r="U20" s="19">
+      <c r="V20" s="16">
         <v>-2.2777926273685409</v>
       </c>
-      <c r="V20" s="19">
+      <c r="W20" s="16">
         <v>-3.3549556243563359</v>
       </c>
-      <c r="W20" s="19">
+      <c r="X20" s="16">
         <v>1.0843977326405252</v>
       </c>
-      <c r="X20" s="19">
+      <c r="Y20" s="16">
         <v>4.834606598944589</v>
       </c>
-      <c r="Y20" s="19">
-        <v>-0.13544258327500813</v>
-      </c>
-      <c r="Z20" s="19">
-        <v>2.0422215906829706</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z20" s="16">
+        <v>-0.14516770735592388</v>
+      </c>
+      <c r="AA20" s="16">
+        <v>2.4690914569471119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="21"/>
+      <c r="C21" s="16">
         <v>-2.1130926829218737</v>
       </c>
-      <c r="C21" s="19">
+      <c r="D21" s="16">
         <v>-1.1447346471100133</v>
       </c>
-      <c r="D21" s="19">
+      <c r="E21" s="16">
         <v>2.9684173571302068</v>
       </c>
-      <c r="E21" s="19">
+      <c r="F21" s="16">
         <v>3.7247219415388173</v>
       </c>
-      <c r="F21" s="19">
+      <c r="G21" s="16">
         <v>2.4196975714203717</v>
       </c>
-      <c r="G21" s="19">
+      <c r="H21" s="16">
         <v>3.228181507229877</v>
       </c>
-      <c r="H21" s="19">
+      <c r="I21" s="16">
         <v>4.3819464398488179</v>
       </c>
-      <c r="I21" s="19">
+      <c r="J21" s="16">
         <v>1.7970228462450137</v>
       </c>
-      <c r="J21" s="19">
+      <c r="K21" s="16">
         <v>11.585357423784771</v>
       </c>
-      <c r="K21" s="19">
+      <c r="L21" s="16">
         <v>-9.2015147912060371</v>
       </c>
-      <c r="L21" s="19">
+      <c r="M21" s="16">
         <v>1.2968854850549718</v>
       </c>
-      <c r="M21" s="19">
+      <c r="N21" s="16">
         <v>5.4471814074426845</v>
       </c>
-      <c r="N21" s="19">
+      <c r="O21" s="16">
         <v>4.9592600255184749</v>
       </c>
-      <c r="O21" s="19">
+      <c r="P21" s="16">
         <v>5.263287767835493</v>
       </c>
-      <c r="P21" s="19">
+      <c r="Q21" s="16">
         <v>2.7972066338091537</v>
       </c>
-      <c r="Q21" s="19">
+      <c r="R21" s="16">
         <v>1.8480352424427053</v>
       </c>
-      <c r="R21" s="19">
+      <c r="S21" s="16">
         <v>7.6950196900672978</v>
       </c>
-      <c r="S21" s="19">
+      <c r="T21" s="16">
         <v>3.9541475454877002</v>
       </c>
-      <c r="T21" s="19">
+      <c r="U21" s="16">
         <v>2.0138759935666428</v>
       </c>
-      <c r="U21" s="19">
+      <c r="V21" s="16">
         <v>-0.6582599295388718</v>
       </c>
-      <c r="V21" s="19">
+      <c r="W21" s="16">
         <v>-6.4126759595213372</v>
       </c>
-      <c r="W21" s="19">
+      <c r="X21" s="16">
         <v>0.16823524681539936</v>
       </c>
-      <c r="X21" s="19">
+      <c r="Y21" s="16">
         <v>3.1642172890647942</v>
       </c>
-      <c r="Y21" s="19">
-        <v>2.1716506377891278</v>
-      </c>
-      <c r="Z21" s="19">
-        <v>-1.2053853451438528</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z21" s="16">
+        <v>2.2129031785263322</v>
+      </c>
+      <c r="AA21" s="16">
+        <v>-1.431428404580231</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="21">
+        <v>114.57247636579645</v>
+      </c>
+      <c r="C22" s="16">
         <v>116.20635926320202</v>
       </c>
-      <c r="C22" s="19">
+      <c r="D22" s="16">
         <v>117.12990792354017</v>
       </c>
-      <c r="D22" s="19">
+      <c r="E22" s="16">
         <v>119.98930342540297</v>
       </c>
-      <c r="E22" s="19">
+      <c r="F22" s="16">
         <v>124.07653207774113</v>
       </c>
-      <c r="F22" s="19">
+      <c r="G22" s="16">
         <v>125.8255668112445</v>
       </c>
-      <c r="G22" s="19">
+      <c r="H22" s="16">
         <v>131.39711867036053</v>
       </c>
-      <c r="H22" s="19">
+      <c r="I22" s="16">
         <v>134.45600619184674</v>
       </c>
-      <c r="I22" s="19">
+      <c r="J22" s="16">
         <v>138.55462853299048</v>
       </c>
-      <c r="J22" s="19">
+      <c r="K22" s="16">
         <v>138.78458942576452</v>
       </c>
-      <c r="K22" s="19">
+      <c r="L22" s="16">
         <v>143.19979005532826</v>
       </c>
-      <c r="L22" s="19">
+      <c r="M22" s="16">
         <v>145.96820920559864</v>
       </c>
-      <c r="M22" s="19">
+      <c r="N22" s="16">
         <v>154.29179345504338</v>
       </c>
-      <c r="N22" s="19">
+      <c r="O22" s="16">
         <v>161.2710826746237</v>
       </c>
-      <c r="O22" s="19">
+      <c r="P22" s="16">
         <v>172.92690740496403</v>
       </c>
-      <c r="P22" s="19">
+      <c r="Q22" s="16">
         <v>179.55122491752701</v>
       </c>
-      <c r="Q22" s="19">
+      <c r="R22" s="16">
         <v>178.3294308601516</v>
       </c>
-      <c r="R22" s="19">
+      <c r="S22" s="16">
         <v>197.8972229466317</v>
       </c>
-      <c r="S22" s="19">
+      <c r="T22" s="16">
         <v>202.61580360798473</v>
       </c>
-      <c r="T22" s="19">
+      <c r="U22" s="16">
         <v>210.62732932470232</v>
       </c>
-      <c r="U22" s="19">
+      <c r="V22" s="16">
         <v>223.25056757014036</v>
       </c>
-      <c r="V22" s="19">
+      <c r="W22" s="16">
         <v>204.84725833818965</v>
       </c>
-      <c r="W22" s="19">
+      <c r="X22" s="16">
         <v>202.82993582416788</v>
       </c>
-      <c r="X22" s="19">
+      <c r="Y22" s="16">
         <v>209.39260567101309</v>
       </c>
-      <c r="Y22" s="19">
-        <v>214.33812568807002</v>
-      </c>
-      <c r="Z22" s="19">
-        <v>223.84278425504519</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="Z22" s="16">
+        <v>214.35221707135719</v>
+      </c>
+      <c r="AA22" s="16">
+        <v>223.49141775633996</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
       <c r="F23" s="16"/>
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
       <c r="I23" s="16"/>
       <c r="J23" s="16"/>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="16"/>
+      <c r="T23" s="16"/>
+      <c r="U23" s="16"/>
+      <c r="V23" s="16"/>
+      <c r="W23" s="16"/>
+      <c r="X23" s="16"/>
+      <c r="Y23" s="16"/>
+      <c r="Z23" s="16"/>
+      <c r="AA23" s="16"/>
+    </row>
+    <row r="24" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="21"/>
+      <c r="C24" s="16">
         <v>0.53572493566903168</v>
       </c>
-      <c r="C24" s="19">
+      <c r="D24" s="16">
         <v>0.50391690281226276</v>
       </c>
-      <c r="D24" s="19">
+      <c r="E24" s="16">
         <v>0.63824461221791473</v>
       </c>
-      <c r="E24" s="19">
+      <c r="F24" s="16">
         <v>0.69317816347499106</v>
       </c>
-      <c r="F24" s="19">
+      <c r="G24" s="16">
         <v>0.47922417929554068</v>
       </c>
-      <c r="G24" s="19">
+      <c r="H24" s="16">
         <v>0.61735921528388871</v>
       </c>
-      <c r="H24" s="19">
+      <c r="I24" s="16">
         <v>0.72253555266598279</v>
       </c>
-      <c r="I24" s="19">
+      <c r="J24" s="16">
         <v>0.45204474644603559</v>
       </c>
-      <c r="J24" s="19">
+      <c r="K24" s="16">
         <v>-1.9061907672865679E-2</v>
       </c>
-      <c r="K24" s="19">
+      <c r="L24" s="16">
         <v>0.16800374717343552</v>
       </c>
-      <c r="L24" s="19">
+      <c r="M24" s="16">
         <v>0.40648931854393122</v>
       </c>
-      <c r="M24" s="19">
+      <c r="N24" s="16">
         <v>0.37011150912952245</v>
       </c>
-      <c r="N24" s="19">
+      <c r="O24" s="16">
         <v>0.33935969503082891</v>
       </c>
-      <c r="O24" s="19">
+      <c r="P24" s="16">
         <v>0.2076344698626689</v>
       </c>
-      <c r="P24" s="19">
+      <c r="Q24" s="16">
         <v>7.8292518559257965E-2</v>
       </c>
-      <c r="Q24" s="19">
+      <c r="R24" s="16">
         <v>-9.7228129960775039E-2</v>
       </c>
-      <c r="R24" s="19">
+      <c r="S24" s="16">
         <v>0.39775284144135592</v>
       </c>
-      <c r="S24" s="19">
+      <c r="T24" s="16">
         <v>0.10208537910077918</v>
       </c>
-      <c r="T24" s="19">
+      <c r="U24" s="16">
         <v>0.10507759769818953</v>
       </c>
-      <c r="U24" s="19">
+      <c r="V24" s="16">
         <v>-1.6266387577669711E-2</v>
       </c>
-      <c r="V24" s="19">
+      <c r="W24" s="16">
         <v>-2.746973498739998E-2</v>
       </c>
-      <c r="W24" s="19">
+      <c r="X24" s="16">
         <v>4.4445266902757456E-2</v>
       </c>
-      <c r="X24" s="19">
+      <c r="Y24" s="16">
         <v>0.10192828700729931</v>
       </c>
-      <c r="Y24" s="19">
-        <v>-0.11596456502639445</v>
-      </c>
-      <c r="Z24" s="19">
-        <v>0.21901636414747241</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z24" s="16">
+        <v>-0.11697613308159985</v>
+      </c>
+      <c r="AA24" s="16">
+        <v>0.21911479106553627</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="21"/>
+      <c r="C25" s="16">
         <v>0.38936980518853426</v>
       </c>
-      <c r="C25" s="19">
+      <c r="D25" s="16">
         <v>1.0511038421535999</v>
       </c>
-      <c r="D25" s="19">
+      <c r="E25" s="16">
         <v>1.4193792693597891</v>
       </c>
-      <c r="E25" s="19">
+      <c r="F25" s="16">
         <v>1.2594057261011684</v>
       </c>
-      <c r="F25" s="19">
+      <c r="G25" s="16">
         <v>1.4158521664202144</v>
       </c>
-      <c r="G25" s="19">
+      <c r="H25" s="16">
         <v>1.0441114238417433</v>
       </c>
-      <c r="H25" s="19">
+      <c r="I25" s="16">
         <v>1.3703022350206995</v>
       </c>
-      <c r="I25" s="19">
+      <c r="J25" s="16">
         <v>1.4964227363152931</v>
       </c>
-      <c r="J25" s="19">
+      <c r="K25" s="16">
         <v>-0.39032857392431808</v>
       </c>
-      <c r="K25" s="19">
+      <c r="L25" s="16">
         <v>2.5754614965030496</v>
       </c>
-      <c r="L25" s="19">
+      <c r="M25" s="16">
         <v>0.43076827634088488</v>
       </c>
-      <c r="M25" s="19">
+      <c r="N25" s="16">
         <v>2.0328300999933719</v>
       </c>
-      <c r="N25" s="19">
+      <c r="O25" s="16">
         <v>1.8126790818738667</v>
       </c>
-      <c r="O25" s="19">
+      <c r="P25" s="16">
         <v>1.9834009780286852</v>
       </c>
-      <c r="P25" s="19">
+      <c r="Q25" s="16">
         <v>1.7420781108858632</v>
       </c>
-      <c r="Q25" s="19">
+      <c r="R25" s="16">
         <v>2.2003668526029965</v>
       </c>
-      <c r="R25" s="19">
+      <c r="S25" s="16">
         <v>1.9103508557717972</v>
       </c>
-      <c r="S25" s="19">
+      <c r="T25" s="16">
         <v>1.9908784525920282</v>
       </c>
-      <c r="T25" s="19">
+      <c r="U25" s="16">
         <v>1.5106775013443499</v>
       </c>
-      <c r="U25" s="19">
+      <c r="V25" s="16">
         <v>-3.6271740807302244</v>
       </c>
-      <c r="V25" s="19">
+      <c r="W25" s="16">
         <v>2.3136376439532196</v>
       </c>
-      <c r="W25" s="19">
+      <c r="X25" s="16">
         <v>1.8880970187936481</v>
       </c>
-      <c r="X25" s="19">
+      <c r="Y25" s="16">
         <v>1.0177013095465106</v>
       </c>
-      <c r="Y25" s="19">
-        <v>1.4854386351558211</v>
-      </c>
-      <c r="Z25" s="19">
-        <v>0.39374978826718887</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z25" s="16">
+        <v>1.4827291014489006</v>
+      </c>
+      <c r="AA25" s="16">
+        <v>0.44093372299179828</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="21"/>
+      <c r="C26" s="16">
         <v>1.8504590452513812</v>
       </c>
-      <c r="C26" s="19">
+      <c r="D26" s="16">
         <v>1.8257780849386434</v>
       </c>
-      <c r="D26" s="19">
+      <c r="E26" s="16">
         <v>2.569956502192603</v>
       </c>
-      <c r="E26" s="19">
+      <c r="F26" s="16">
         <v>4.0279193917259359</v>
       </c>
-      <c r="F26" s="19">
+      <c r="G26" s="16">
         <v>2.609877305970119</v>
       </c>
-      <c r="G26" s="19">
+      <c r="H26" s="16">
         <v>3.1697761681711611</v>
       </c>
-      <c r="H26" s="19">
+      <c r="I26" s="16">
         <v>3.8643099852372975</v>
       </c>
-      <c r="I26" s="19">
+      <c r="J26" s="16">
         <v>2.0287340745666818</v>
       </c>
-      <c r="J26" s="19">
+      <c r="K26" s="16">
         <v>1.7313786045607027</v>
       </c>
-      <c r="K26" s="19">
+      <c r="L26" s="16">
         <v>3.8092304615186348</v>
       </c>
-      <c r="L26" s="19">
+      <c r="M26" s="16">
         <v>2.6185961857087849</v>
       </c>
-      <c r="M26" s="19">
+      <c r="N26" s="16">
         <v>3.8056306389726591</v>
       </c>
-      <c r="N26" s="19">
+      <c r="O26" s="16">
         <v>3.9154220270630287</v>
       </c>
-      <c r="O26" s="19">
+      <c r="P26" s="16">
         <v>3.4784813853901726</v>
       </c>
-      <c r="P26" s="19">
+      <c r="Q26" s="16">
         <v>3.8583700030519132</v>
       </c>
-      <c r="Q26" s="19">
+      <c r="R26" s="16">
         <v>4.3060806425462843</v>
       </c>
-      <c r="R26" s="19">
+      <c r="S26" s="16">
         <v>3.9244565176619588</v>
       </c>
-      <c r="S26" s="19">
+      <c r="T26" s="16">
         <v>3.6144317862517052</v>
       </c>
-      <c r="T26" s="19">
+      <c r="U26" s="16">
         <v>3.913341780773806</v>
       </c>
-      <c r="U26" s="19">
+      <c r="V26" s="16">
         <v>-5.0184897755173976</v>
       </c>
-      <c r="V26" s="19">
+      <c r="W26" s="16">
         <v>3.0285001314326578</v>
       </c>
-      <c r="W26" s="19">
+      <c r="X26" s="16">
         <v>5.3957370599531984</v>
       </c>
-      <c r="X26" s="19">
+      <c r="Y26" s="16">
         <v>4.1033859429299371</v>
       </c>
-      <c r="Y26" s="19">
-        <v>3.7791492762411636</v>
-      </c>
-      <c r="Z26" s="19">
-        <v>3.2965400857662495</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z26" s="16">
+        <v>3.8034296566129355</v>
+      </c>
+      <c r="AA26" s="16">
+        <v>3.2500548165465566</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="21"/>
+      <c r="C27" s="16">
         <v>0.33193422964826325</v>
       </c>
-      <c r="C27" s="19">
+      <c r="D27" s="16">
         <v>0.33880011992618214</v>
       </c>
-      <c r="D27" s="19">
+      <c r="E27" s="16">
         <v>0.38107166909579449</v>
       </c>
-      <c r="E27" s="19">
+      <c r="F27" s="16">
         <v>0.46124180549936711</v>
       </c>
-      <c r="F27" s="19">
+      <c r="G27" s="16">
         <v>0.75287964458213052</v>
       </c>
-      <c r="G27" s="19">
+      <c r="H27" s="16">
         <v>-9.4686799766790966E-2</v>
       </c>
-      <c r="H27" s="19">
+      <c r="I27" s="16">
         <v>0.3658396457837757</v>
       </c>
-      <c r="I27" s="19">
+      <c r="J27" s="16">
         <v>0.6745425927422174</v>
       </c>
-      <c r="J27" s="19">
+      <c r="K27" s="16">
         <v>2.3251916574617759</v>
       </c>
-      <c r="K27" s="19">
+      <c r="L27" s="16">
         <v>0.50598824273614795</v>
       </c>
-      <c r="L27" s="19">
+      <c r="M27" s="16">
         <v>-0.1147010304288556</v>
       </c>
-      <c r="M27" s="19">
+      <c r="N27" s="16">
         <v>0.85231814608388767</v>
       </c>
-      <c r="N27" s="19">
+      <c r="O27" s="16">
         <v>1.363406501764677</v>
       </c>
-      <c r="O27" s="19">
+      <c r="P27" s="16">
         <v>0.51112259817264438</v>
       </c>
-      <c r="P27" s="19">
+      <c r="Q27" s="16">
         <v>0.44008262841733709</v>
       </c>
-      <c r="Q27" s="19">
+      <c r="R27" s="16">
         <v>0.41033227645540099</v>
       </c>
-      <c r="R27" s="19">
+      <c r="S27" s="16">
         <v>0.6059756616498263</v>
       </c>
-      <c r="S27" s="19">
+      <c r="T27" s="16">
         <v>0.20389934228312756</v>
       </c>
-      <c r="T27" s="19">
+      <c r="U27" s="16">
         <v>-0.15276223202214745</v>
       </c>
-      <c r="U27" s="19">
+      <c r="V27" s="16">
         <v>-2.7987621988806208</v>
       </c>
-      <c r="V27" s="19">
+      <c r="W27" s="16">
         <v>-3.6104035063311235</v>
       </c>
-      <c r="W27" s="19">
+      <c r="X27" s="16">
         <v>2.5589349692959829</v>
       </c>
-      <c r="X27" s="19">
+      <c r="Y27" s="16">
         <v>5.1773073804286156</v>
       </c>
-      <c r="Y27" s="19">
-        <v>2.5362180893583552</v>
-      </c>
-      <c r="Z27" s="19">
-        <v>2.1450298031547304</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z27" s="16">
+        <v>2.4927048092835498</v>
+      </c>
+      <c r="AA27" s="16">
+        <v>2.2013904240232316</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="21"/>
+      <c r="C28" s="16">
         <v>3.1074880157572107</v>
       </c>
-      <c r="C28" s="19">
+      <c r="D28" s="16">
         <v>3.7195989498306883</v>
       </c>
-      <c r="D28" s="19">
+      <c r="E28" s="16">
         <v>5.0086520528661005</v>
       </c>
-      <c r="E28" s="19">
+      <c r="F28" s="16">
         <v>6.4417450868014621</v>
       </c>
-      <c r="F28" s="19">
+      <c r="G28" s="16">
         <v>5.2578332962680046</v>
       </c>
-      <c r="G28" s="19">
+      <c r="H28" s="16">
         <v>4.7365600075300023</v>
       </c>
-      <c r="H28" s="19">
+      <c r="I28" s="16">
         <v>6.3229874187077559</v>
       </c>
-      <c r="I28" s="19">
+      <c r="J28" s="16">
         <v>4.6517441500702281</v>
       </c>
-      <c r="J28" s="19">
+      <c r="K28" s="16">
         <v>3.6471797804252946</v>
       </c>
-      <c r="K28" s="19">
+      <c r="L28" s="16">
         <v>7.058683947931268</v>
       </c>
-      <c r="L28" s="19">
+      <c r="M28" s="16">
         <v>3.3411527501647456</v>
       </c>
-      <c r="M28" s="19">
+      <c r="N28" s="16">
         <v>7.0608903941794408</v>
       </c>
-      <c r="N28" s="19">
+      <c r="O28" s="16">
         <v>7.4308673057324022</v>
       </c>
-      <c r="O28" s="19">
+      <c r="P28" s="16">
         <v>6.1806394314541713</v>
       </c>
-      <c r="P28" s="19">
+      <c r="Q28" s="16">
         <v>6.1188232609143718</v>
       </c>
-      <c r="Q28" s="19">
+      <c r="R28" s="16">
         <v>6.8195516416439066</v>
       </c>
-      <c r="R28" s="19">
+      <c r="S28" s="16">
         <v>6.8385358765249382</v>
       </c>
-      <c r="S28" s="19">
+      <c r="T28" s="16">
         <v>5.9112949602276403</v>
       </c>
-      <c r="T28" s="19">
+      <c r="U28" s="16">
         <v>5.3763346477941978</v>
       </c>
-      <c r="U28" s="19">
+      <c r="V28" s="16">
         <v>-11.460692442705913</v>
       </c>
-      <c r="V28" s="19">
+      <c r="W28" s="16">
         <v>1.7042645340673541</v>
       </c>
-      <c r="W28" s="19">
+      <c r="X28" s="16">
         <v>9.887214314945588</v>
       </c>
-      <c r="X28" s="19">
+      <c r="Y28" s="16">
         <v>10.400322919912362</v>
       </c>
-      <c r="Y28" s="19">
-        <v>7.684841435728945</v>
-      </c>
-      <c r="Z28" s="19">
-        <v>6.0543360413356409</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z28" s="16">
+        <v>7.6618874342637859</v>
+      </c>
+      <c r="AA28" s="16">
+        <v>6.1114937546271229</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="21">
+        <v>123.19250059124917</v>
+      </c>
+      <c r="C29" s="16">
         <v>124.11442269442851</v>
       </c>
-      <c r="C29" s="19">
+      <c r="D29" s="16">
         <v>122.9687831357716</v>
       </c>
-      <c r="D29" s="19">
+      <c r="E29" s="16">
         <v>121.40300508159079</v>
       </c>
-      <c r="E29" s="19">
+      <c r="F29" s="16">
         <v>116.29935406055189</v>
       </c>
-      <c r="F29" s="19">
+      <c r="G29" s="16">
         <v>112.35662358918717</v>
       </c>
-      <c r="G29" s="19">
+      <c r="H29" s="16">
         <v>110.32235209721331</v>
       </c>
-      <c r="H29" s="19">
+      <c r="I29" s="16">
         <v>109.60546726128445</v>
       </c>
-      <c r="I29" s="19">
+      <c r="J29" s="16">
         <v>109.31268912996424</v>
       </c>
-      <c r="J29" s="19">
+      <c r="K29" s="16">
         <v>113.587844564939</v>
       </c>
-      <c r="K29" s="19">
+      <c r="L29" s="16">
         <v>114.45633748023032</v>
       </c>
-      <c r="L29" s="19">
+      <c r="M29" s="16">
         <v>106.08779004087087</v>
       </c>
-      <c r="M29" s="19">
+      <c r="N29" s="16">
         <v>106.69796566288923</v>
       </c>
-      <c r="N29" s="19">
+      <c r="O29" s="16">
         <v>109.32572364512166</v>
       </c>
-      <c r="O29" s="19">
+      <c r="P29" s="16">
         <v>110.22705932045365</v>
       </c>
-      <c r="P29" s="19">
+      <c r="Q29" s="16">
         <v>108.12914791603279</v>
       </c>
-      <c r="Q29" s="19">
+      <c r="R29" s="16">
         <v>104.91448132896528</v>
       </c>
-      <c r="R29" s="19">
+      <c r="S29" s="16">
         <v>103.63394507254478</v>
       </c>
-      <c r="S29" s="19">
+      <c r="T29" s="16">
         <v>100.00000000000004</v>
       </c>
-      <c r="T29" s="19">
+      <c r="U29" s="16">
         <v>97.114865305624917</v>
       </c>
-      <c r="U29" s="19">
+      <c r="V29" s="16">
         <v>99.003010831905627</v>
       </c>
-      <c r="V29" s="19">
+      <c r="W29" s="16">
         <v>92.324154535149631</v>
       </c>
-      <c r="W29" s="19">
+      <c r="X29" s="16">
         <v>89.594309282219555</v>
       </c>
-      <c r="X29" s="19">
+      <c r="Y29" s="16">
         <v>90.520623891965187</v>
       </c>
-      <c r="Y29" s="19">
-        <v>89.807891774966578</v>
-      </c>
-      <c r="Z29" s="19">
-        <v>90.465097043109495</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z29" s="16">
+        <v>89.81476401762373</v>
+      </c>
+      <c r="AA29" s="16">
+        <v>89.65294860183505</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="20">
+        <v>398690.34392726875</v>
+      </c>
+      <c r="C30" s="15">
         <v>433192.35062264308</v>
       </c>
-      <c r="C30" s="18">
+      <c r="D30" s="15">
         <v>442174.84754561534</v>
       </c>
-      <c r="D30" s="18">
+      <c r="E30" s="15">
         <v>440478.02063484181</v>
       </c>
-      <c r="E30" s="18">
+      <c r="F30" s="15">
         <v>360011.35489322367</v>
       </c>
-      <c r="F30" s="18">
+      <c r="G30" s="15">
         <v>297552.13961732591</v>
       </c>
-      <c r="G30" s="18">
+      <c r="H30" s="15">
         <v>263757.09106253367</v>
       </c>
-      <c r="H30" s="18">
+      <c r="I30" s="15">
         <v>251452.26635724216</v>
       </c>
-      <c r="I30" s="18">
+      <c r="J30" s="15">
         <v>244275.66443956774</v>
       </c>
-      <c r="J30" s="18">
+      <c r="K30" s="15">
         <v>336900.12566521129</v>
       </c>
-      <c r="K30" s="18">
+      <c r="L30" s="15">
         <v>431819.76269039814</v>
       </c>
-      <c r="L30" s="18">
+      <c r="M30" s="15">
         <v>195299.13459711592</v>
       </c>
-      <c r="M30" s="18">
+      <c r="N30" s="15">
         <v>219320.69736100943</v>
       </c>
-      <c r="N30" s="18">
+      <c r="O30" s="15">
         <v>321303.60006254388</v>
       </c>
-      <c r="O30" s="18">
+      <c r="P30" s="15">
         <v>386287.51980568806</v>
       </c>
-      <c r="P30" s="18">
+      <c r="Q30" s="15">
         <v>354583.60669640487</v>
       </c>
-      <c r="Q30" s="18">
+      <c r="R30" s="15">
         <v>246400.54259697616</v>
       </c>
-      <c r="R30" s="18">
+      <c r="S30" s="15">
         <v>212998.71032233437</v>
       </c>
-      <c r="S30" s="18">
+      <c r="T30" s="15">
         <v>-983.63566984597128</v>
       </c>
-      <c r="T30" s="18">
+      <c r="U30" s="15">
         <v>-191545.63239015336</v>
       </c>
-      <c r="U30" s="18">
+      <c r="V30" s="15">
         <v>-52610.987692413735</v>
       </c>
-      <c r="V30" s="18">
+      <c r="W30" s="15">
         <v>-479238.33422542206</v>
       </c>
-      <c r="W30" s="18">
+      <c r="X30" s="15">
         <v>-757271.57696092478</v>
       </c>
-      <c r="X30" s="18">
-        <v>-688251.0006017437</v>
-      </c>
-      <c r="Y30" s="18">
-        <v>-768473.2722657501</v>
-      </c>
-      <c r="Z30" s="18">
-        <v>-769625.39020690694</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y30" s="15">
+        <v>-688251.00060174323</v>
+      </c>
+      <c r="Z30" s="15">
+        <v>-767858.24515834288</v>
+      </c>
+      <c r="AA30" s="15">
+        <v>-839279.77224524145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="16"/>
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
       <c r="I31" s="16"/>
       <c r="J31" s="16"/>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="16"/>
+      <c r="R31" s="16"/>
+      <c r="S31" s="16"/>
+      <c r="T31" s="16"/>
+      <c r="U31" s="16"/>
+      <c r="V31" s="16"/>
+      <c r="W31" s="16"/>
+      <c r="X31" s="16"/>
+      <c r="Y31" s="16"/>
+      <c r="Z31" s="16"/>
+      <c r="AA31" s="16"/>
+    </row>
+    <row r="32" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
       <c r="F32" s="16"/>
       <c r="G32" s="16"/>
       <c r="H32" s="16"/>
       <c r="I32" s="16"/>
       <c r="J32" s="16"/>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="16"/>
+      <c r="S32" s="16"/>
+      <c r="T32" s="16"/>
+      <c r="U32" s="16"/>
+      <c r="V32" s="16"/>
+      <c r="W32" s="16"/>
+      <c r="X32" s="16"/>
+      <c r="Y32" s="16"/>
+      <c r="Z32" s="16"/>
+      <c r="AA32" s="16"/>
+    </row>
+    <row r="33" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="20">
+        <v>56760.07554653706</v>
+      </c>
+      <c r="C33" s="15">
         <v>-104207.20699449349</v>
       </c>
-      <c r="C33" s="18">
+      <c r="D33" s="15">
         <v>-166776.28146070684</v>
       </c>
-      <c r="D33" s="18">
+      <c r="E33" s="15">
         <v>-139864.52338779136</v>
       </c>
-      <c r="E33" s="18">
+      <c r="F33" s="15">
         <v>-184824.80870771641</v>
       </c>
-      <c r="F33" s="18">
+      <c r="G33" s="15">
         <v>-81989.635114453733</v>
       </c>
-      <c r="G33" s="18">
+      <c r="H33" s="15">
         <v>107451.73675115826</v>
       </c>
-      <c r="H33" s="18">
+      <c r="I33" s="15">
         <v>171562.44199630059</v>
       </c>
-      <c r="I33" s="18">
+      <c r="J33" s="15">
         <v>-77877.985834633</v>
       </c>
-      <c r="J33" s="18">
+      <c r="K33" s="15">
         <v>-37550.457626908552</v>
       </c>
-      <c r="K33" s="18">
+      <c r="L33" s="15">
         <v>-33332.245267331135</v>
       </c>
-      <c r="L33" s="18">
+      <c r="M33" s="15">
         <v>-262237.35920881387</v>
       </c>
-      <c r="M33" s="18">
+      <c r="N33" s="15">
         <v>-321626.19483880466</v>
       </c>
-      <c r="N33" s="18">
+      <c r="O33" s="15">
         <v>-418148.50600552093</v>
       </c>
-      <c r="O33" s="18">
+      <c r="P33" s="15">
         <v>-364398.01172742946</v>
       </c>
-      <c r="P33" s="18">
+      <c r="Q33" s="15">
         <v>-658928.04048938211</v>
       </c>
-      <c r="Q33" s="18">
+      <c r="R33" s="15">
         <v>-1275668.6979825203</v>
       </c>
-      <c r="R33" s="18">
+      <c r="S33" s="15">
         <v>-1500659.7595624719</v>
       </c>
-      <c r="S33" s="18">
+      <c r="T33" s="15">
         <v>-2143636.9855572022</v>
       </c>
-      <c r="T33" s="18">
+      <c r="U33" s="15">
         <v>-2356977.592620736</v>
       </c>
-      <c r="U33" s="18">
+      <c r="V33" s="15">
         <v>-1393738.9319944549</v>
       </c>
-      <c r="V33" s="18">
+      <c r="W33" s="15">
         <v>-2325496.4291233122</v>
       </c>
-      <c r="W33" s="18">
+      <c r="X33" s="15">
         <v>-3448500.3410781333</v>
       </c>
-      <c r="X33" s="18">
+      <c r="Y33" s="15">
         <v>-3439462.4476467725</v>
       </c>
-      <c r="Y33" s="18">
-        <v>-3792036.5496865455</v>
-      </c>
-      <c r="Z33" s="18">
-        <v>-3749444.1978886165</v>
-      </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z33" s="15">
+        <v>-3806029.113550676</v>
+      </c>
+      <c r="AA33" s="15">
+        <v>-3835381.7997070886</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="22">
+        <v>1.5350699865989372</v>
+      </c>
+      <c r="C34" s="16">
         <v>-2.5893856087173024</v>
       </c>
-      <c r="C34" s="19">
+      <c r="D34" s="16">
         <v>-3.8334442047880177</v>
       </c>
-      <c r="D34" s="19">
+      <c r="E34" s="16">
         <v>-2.9646076208717229</v>
       </c>
-      <c r="E34" s="19">
+      <c r="F34" s="16">
         <v>-3.4716028417498777</v>
       </c>
-      <c r="F34" s="19">
+      <c r="G34" s="16">
         <v>-1.3855961392659126</v>
       </c>
-      <c r="G34" s="19">
+      <c r="H34" s="16">
         <v>1.6403800689145824</v>
       </c>
-      <c r="H34" s="19">
+      <c r="I34" s="16">
         <v>2.3833926835126431</v>
       </c>
-      <c r="I34" s="19">
+      <c r="J34" s="16">
         <v>-0.96740428599570494</v>
       </c>
-      <c r="J34" s="19">
+      <c r="K34" s="16">
         <v>-0.44753958811979422</v>
       </c>
-      <c r="K34" s="19">
+      <c r="L34" s="16">
         <v>-0.35461907429750078</v>
       </c>
-      <c r="L34" s="19">
+      <c r="M34" s="16">
         <v>-2.5849789437180313</v>
       </c>
-      <c r="M34" s="19">
+      <c r="N34" s="16">
         <v>-2.907857798220888</v>
       </c>
-      <c r="N34" s="19">
+      <c r="O34" s="16">
         <v>-3.4699416140856005</v>
       </c>
-      <c r="O34" s="19">
+      <c r="P34" s="16">
         <v>-2.7591637051897449</v>
       </c>
-      <c r="P34" s="19">
+      <c r="Q34" s="16">
         <v>-4.7254776271549659</v>
       </c>
-      <c r="Q34" s="19">
+      <c r="R34" s="16">
         <v>-8.4300590789158072</v>
       </c>
-      <c r="R34" s="19">
+      <c r="S34" s="16">
         <v>-9.0637880330935108</v>
       </c>
-      <c r="S34" s="19">
+      <c r="T34" s="16">
         <v>-11.736187552710131</v>
       </c>
-      <c r="T34" s="19">
+      <c r="U34" s="16">
         <v>-12.07600223389421</v>
       </c>
-      <c r="U34" s="19">
+      <c r="V34" s="16">
         <v>-7.7638816817854437</v>
       </c>
-      <c r="V34" s="19">
+      <c r="W34" s="16">
         <v>-11.980539981249109</v>
       </c>
-      <c r="W34" s="19">
+      <c r="X34" s="16">
         <v>-15.654880519103937</v>
       </c>
-      <c r="X34" s="19">
+      <c r="Y34" s="16">
         <v>-14.146270623043703</v>
       </c>
-      <c r="Y34" s="19">
-        <v>-14.338590219059522</v>
-      </c>
-      <c r="Z34" s="19">
-        <v>-13.384053707901659</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z34" s="16">
+        <v>-14.38982707157197</v>
+      </c>
+      <c r="AA34" s="16">
+        <v>-13.692933697284726</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="18">
+      <c r="B35" s="20">
+        <v>152292.87523546</v>
+      </c>
+      <c r="C35" s="15">
         <v>-35241.290270930389</v>
       </c>
-      <c r="C35" s="18">
+      <c r="D35" s="15">
         <v>-105894.38406062988</v>
       </c>
-      <c r="D35" s="18">
+      <c r="E35" s="15">
         <v>-83216.733195889741</v>
       </c>
-      <c r="E35" s="18">
+      <c r="F35" s="15">
         <v>-128554.84921737015</v>
       </c>
-      <c r="F35" s="18">
+      <c r="G35" s="15">
         <v>-256461.72920380952</v>
       </c>
-      <c r="G35" s="18">
+      <c r="H35" s="15">
         <v>-178469.3693781998</v>
       </c>
-      <c r="H35" s="18">
+      <c r="I35" s="15">
         <v>-146244.15839793906</v>
       </c>
-      <c r="I35" s="18">
+      <c r="J35" s="15">
         <v>-236430.55826286739</v>
       </c>
-      <c r="J35" s="18">
+      <c r="K35" s="15">
         <v>-270880.34317010618</v>
       </c>
-      <c r="K35" s="18">
+      <c r="L35" s="15">
         <v>-407678.93699159008</v>
       </c>
-      <c r="L35" s="18">
+      <c r="M35" s="15">
         <v>-639052.69359568786</v>
       </c>
-      <c r="M35" s="18">
+      <c r="N35" s="15">
         <v>-614363.7610783386</v>
       </c>
-      <c r="N35" s="18">
+      <c r="O35" s="15">
         <v>-754219.99571117968</v>
       </c>
-      <c r="O35" s="18">
+      <c r="P35" s="15">
         <v>-778473.14058652613</v>
       </c>
-      <c r="P35" s="18">
+      <c r="Q35" s="15">
         <v>-1209883.1594135021</v>
       </c>
-      <c r="Q35" s="18">
+      <c r="R35" s="15">
         <v>-1911163.6630118899</v>
       </c>
-      <c r="R35" s="18">
+      <c r="S35" s="15">
         <v>-2343481.9079184453</v>
       </c>
-      <c r="S35" s="18">
+      <c r="T35" s="15">
         <v>-3152044.8759257798</v>
       </c>
-      <c r="T35" s="18">
+      <c r="U35" s="15">
         <v>-3403221.5745688453</v>
       </c>
-      <c r="U35" s="18">
+      <c r="V35" s="15">
         <v>-2238131.5774586778</v>
       </c>
-      <c r="V35" s="18">
+      <c r="W35" s="15">
         <v>-3378857.8126992425</v>
       </c>
-      <c r="W35" s="18">
+      <c r="X35" s="15">
         <v>-4625600.8763994323</v>
       </c>
-      <c r="X35" s="18">
+      <c r="Y35" s="15">
         <v>-4611454.0525397006</v>
       </c>
-      <c r="Y35" s="18">
-        <v>-4953939.9732527984</v>
-      </c>
-      <c r="Z35" s="18">
-        <v>-4841507.111179946</v>
-      </c>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z35" s="15">
+        <v>-4958875.0890571233</v>
+      </c>
+      <c r="AA35" s="15">
+        <v>-4895944.6628805613</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="19">
+      <c r="B36" s="22">
+        <v>85.153368460452455</v>
+      </c>
+      <c r="C36" s="16">
         <v>84.900388623638662</v>
       </c>
-      <c r="C36" s="19">
+      <c r="D36" s="16">
         <v>83.844804092040292</v>
       </c>
-      <c r="D36" s="19">
+      <c r="E36" s="16">
         <v>87.574644362145534</v>
       </c>
-      <c r="E36" s="19">
+      <c r="F36" s="16">
         <v>87.125284824190203</v>
       </c>
-      <c r="F36" s="19">
+      <c r="G36" s="16">
         <v>83.845674571988184</v>
       </c>
-      <c r="G36" s="19">
+      <c r="H36" s="16">
         <v>80.85053867273237</v>
       </c>
-      <c r="H36" s="19">
+      <c r="I36" s="16">
         <v>73.64497999122095</v>
       </c>
-      <c r="I36" s="19">
+      <c r="J36" s="16">
         <v>67.681070773744239</v>
       </c>
-      <c r="J36" s="19">
+      <c r="K36" s="16">
         <v>60.886590786617866</v>
       </c>
-      <c r="K36" s="19">
+      <c r="L36" s="16">
         <v>66.104278514200388</v>
       </c>
-      <c r="L36" s="19">
+      <c r="M36" s="16">
         <v>60.795836699402059</v>
       </c>
-      <c r="M36" s="19">
+      <c r="N36" s="16">
         <v>57.842005513083059</v>
       </c>
-      <c r="N36" s="19">
+      <c r="O36" s="16">
         <v>55.82478123169291</v>
       </c>
-      <c r="O36" s="19">
+      <c r="P36" s="16">
         <v>57.468172087788659</v>
       </c>
-      <c r="P36" s="19">
+      <c r="Q36" s="16">
         <v>59.141592104917372</v>
       </c>
-      <c r="Q36" s="19">
+      <c r="R36" s="16">
         <v>61.776065765495815</v>
       </c>
-      <c r="R36" s="19">
+      <c r="S36" s="16">
         <v>68.168369742669967</v>
       </c>
-      <c r="S36" s="19">
+      <c r="T36" s="16">
         <v>72.163398299406879</v>
       </c>
-      <c r="T36" s="19">
+      <c r="U36" s="16">
         <v>68.841842259576239</v>
       </c>
-      <c r="U36" s="19">
+      <c r="V36" s="16">
         <v>58.16956030179982</v>
       </c>
-      <c r="V36" s="19">
+      <c r="W36" s="16">
         <v>63.48460981380012</v>
       </c>
-      <c r="W36" s="19">
+      <c r="X36" s="16">
         <v>72.429683610981371</v>
       </c>
-      <c r="X36" s="19">
+      <c r="Y36" s="16">
         <v>67.41996931716065</v>
       </c>
-      <c r="Y36" s="19">
-        <v>65.885472528789066</v>
-      </c>
-      <c r="Z36" s="19">
-        <v>66.654331642365534</v>
-      </c>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z36" s="16">
+        <v>65.863788388275111</v>
+      </c>
+      <c r="AA36" s="16">
+        <v>66.793605331434264</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
       <c r="F37" s="16"/>
       <c r="G37" s="16"/>
       <c r="H37" s="16"/>
       <c r="I37" s="16"/>
       <c r="J37" s="16"/>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="16"/>
+      <c r="R37" s="16"/>
+      <c r="S37" s="16"/>
+      <c r="T37" s="16"/>
+      <c r="U37" s="16"/>
+      <c r="V37" s="16"/>
+      <c r="W37" s="16"/>
+      <c r="X37" s="16"/>
+      <c r="Y37" s="16"/>
+      <c r="Z37" s="16"/>
+      <c r="AA37" s="16"/>
+    </row>
+    <row r="38" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="20">
+        <v>1602676.8675764336</v>
+      </c>
+      <c r="C38" s="16">
         <v>1656261.5664936157</v>
       </c>
-      <c r="C38" s="18">
+      <c r="D38" s="16">
         <v>1740471.0181960496</v>
       </c>
-      <c r="D38" s="18">
+      <c r="E38" s="16">
         <v>1995869.9389638093</v>
       </c>
-      <c r="E38" s="18">
+      <c r="F38" s="16">
         <v>2226820.9347223812</v>
       </c>
-      <c r="F38" s="18">
+      <c r="G38" s="16">
         <v>2439697.8133145049</v>
       </c>
-      <c r="G38" s="18">
+      <c r="H38" s="16">
         <v>2701749.6289301077</v>
       </c>
-      <c r="H38" s="18">
+      <c r="I38" s="16">
         <v>2736354.2246547546</v>
       </c>
-      <c r="I38" s="18">
+      <c r="J38" s="16">
         <v>2685291.9968003836</v>
       </c>
-      <c r="J38" s="18">
+      <c r="K38" s="16">
         <v>2535545.559862596</v>
       </c>
-      <c r="K38" s="18">
+      <c r="L38" s="16">
         <v>3090053.4313274845</v>
       </c>
-      <c r="L38" s="18">
+      <c r="M38" s="16">
         <v>2952647.1873643994</v>
       </c>
-      <c r="M38" s="18">
+      <c r="N38" s="16">
         <v>3038020.1031587399</v>
       </c>
-      <c r="N38" s="18">
+      <c r="O38" s="16">
         <v>3154534.0531659303</v>
       </c>
-      <c r="O38" s="18">
+      <c r="P38" s="16">
         <v>3612662.3876467934</v>
       </c>
-      <c r="P38" s="18">
+      <c r="Q38" s="16">
         <v>3793934.3398675267</v>
       </c>
-      <c r="Q38" s="18">
+      <c r="R38" s="16">
         <v>4036260.6154587301</v>
       </c>
-      <c r="R38" s="18">
+      <c r="S38" s="16">
         <v>4892869.6839273497</v>
       </c>
-      <c r="S38" s="18">
+      <c r="T38" s="16">
         <v>5518572.505292261</v>
       </c>
-      <c r="T38" s="18">
+      <c r="U38" s="16">
         <v>5539739.4922342617</v>
       </c>
-      <c r="U38" s="18">
+      <c r="V38" s="16">
         <v>4524306.2404680271</v>
       </c>
-      <c r="V38" s="18">
+      <c r="W38" s="16">
         <v>4998628.2199455351</v>
       </c>
-      <c r="W38" s="18">
+      <c r="X38" s="16">
         <v>6253255.2576194881</v>
       </c>
-      <c r="X38" s="18">
+      <c r="Y38" s="16">
         <v>6476367.1991113052</v>
       </c>
-      <c r="Y38" s="18">
-        <v>6816139.4793562237</v>
-      </c>
-      <c r="Z38" s="18">
-        <v>7461638.2629789859</v>
-      </c>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z38" s="16">
+        <v>6807288.0371227358</v>
+      </c>
+      <c r="AA38" s="16">
+        <v>7436731.7493922096</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="20">
+        <v>36113.971411700724</v>
+      </c>
+      <c r="C39" s="15">
         <v>32535.705698512862</v>
       </c>
-      <c r="C39" s="18">
+      <c r="D39" s="15">
         <v>33680.509471247577</v>
       </c>
-      <c r="D39" s="18">
+      <c r="E39" s="15">
         <v>36810.062890013236</v>
       </c>
-      <c r="E39" s="18">
+      <c r="F39" s="15">
         <v>39731.709418116588</v>
       </c>
-      <c r="F39" s="18">
+      <c r="G39" s="15">
         <v>44285.915147218722</v>
       </c>
-      <c r="G39" s="18">
+      <c r="H39" s="15">
         <v>52678.692643958908</v>
       </c>
-      <c r="H39" s="18">
+      <c r="I39" s="15">
         <v>59408.181223265696</v>
       </c>
-      <c r="I39" s="18">
+      <c r="J39" s="15">
         <v>60536.797480711532</v>
       </c>
-      <c r="J39" s="18">
+      <c r="K39" s="15">
         <v>53231.080664406843</v>
       </c>
-      <c r="K39" s="18">
+      <c r="L39" s="15">
         <v>68500.837574854202</v>
       </c>
-      <c r="L39" s="18">
+      <c r="M39" s="15">
         <v>68170.419145267486</v>
       </c>
-      <c r="M39" s="18">
+      <c r="N39" s="15">
         <v>71932.819113652615</v>
       </c>
-      <c r="N39" s="18">
+      <c r="O39" s="15">
         <v>74847.285312813154</v>
       </c>
-      <c r="O39" s="18">
+      <c r="P39" s="15">
         <v>81425.871130519532</v>
       </c>
-      <c r="P39" s="18">
+      <c r="Q39" s="15">
         <v>83457.865964588113</v>
       </c>
-      <c r="Q39" s="18">
+      <c r="R39" s="15">
         <v>85038.087772176368</v>
       </c>
-      <c r="R39" s="18">
+      <c r="S39" s="15">
         <v>97071.817075608036</v>
       </c>
-      <c r="S39" s="18">
+      <c r="T39" s="15">
         <v>104782.58913012536</v>
       </c>
-      <c r="T39" s="18">
+      <c r="U39" s="15">
         <v>106972.05746026149</v>
       </c>
-      <c r="U39" s="18">
+      <c r="V39" s="15">
         <v>91232.474574672611</v>
       </c>
-      <c r="V39" s="18">
+      <c r="W39" s="15">
         <v>101424.72340094153</v>
       </c>
-      <c r="W39" s="18">
+      <c r="X39" s="15">
         <v>114603.43093771138</v>
       </c>
-      <c r="X39" s="18">
-        <v>116404.75854930759</v>
-      </c>
-      <c r="Y39" s="18">
-        <v>119009.57990885559</v>
-      </c>
-      <c r="Z39" s="18">
-        <v>129678.14611222115</v>
-      </c>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y39" s="15">
+        <v>116404.7585493076</v>
+      </c>
+      <c r="Z39" s="15">
+        <v>118855.47461168139</v>
+      </c>
+      <c r="AA39" s="15">
+        <v>129244.85874411295</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="19">
+      <c r="B40" s="22">
+        <v>43.344219223525698</v>
+      </c>
+      <c r="C40" s="16">
         <v>41.155501507460684</v>
       </c>
-      <c r="C40" s="19">
+      <c r="D40" s="16">
         <v>40.005679943626134</v>
       </c>
-      <c r="D40" s="19">
+      <c r="E40" s="16">
         <v>42.305018370636908</v>
       </c>
-      <c r="E40" s="19">
+      <c r="F40" s="16">
         <v>41.826840991220159</v>
       </c>
-      <c r="F40" s="19">
+      <c r="G40" s="16">
         <v>41.230039216361135</v>
       </c>
-      <c r="G40" s="19">
+      <c r="H40" s="16">
         <v>41.245459370823475</v>
       </c>
-      <c r="H40" s="19">
+      <c r="I40" s="16">
         <v>38.014186337366795</v>
       </c>
-      <c r="I40" s="19">
+      <c r="J40" s="16">
         <v>33.35683324387427</v>
       </c>
-      <c r="J40" s="19">
+      <c r="K40" s="16">
         <v>30.219525599249032</v>
       </c>
-      <c r="K40" s="19">
+      <c r="L40" s="16">
         <v>32.874829719951443</v>
       </c>
-      <c r="L40" s="19">
+      <c r="M40" s="16">
         <v>29.105428877842016</v>
       </c>
-      <c r="M40" s="19">
+      <c r="N40" s="16">
         <v>27.467073857431089</v>
       </c>
-      <c r="N40" s="19">
+      <c r="O40" s="16">
         <v>26.177419808803659</v>
       </c>
-      <c r="O40" s="19">
+      <c r="P40" s="16">
         <v>27.354504191299455</v>
       </c>
-      <c r="P40" s="19">
+      <c r="Q40" s="16">
         <v>27.208057238881207</v>
       </c>
-      <c r="Q40" s="19">
+      <c r="R40" s="16">
         <v>26.673003343290002</v>
       </c>
-      <c r="R40" s="19">
+      <c r="S40" s="16">
         <v>29.552290854788225</v>
       </c>
-      <c r="S40" s="19">
+      <c r="T40" s="16">
         <v>30.213605373348372</v>
       </c>
-      <c r="T40" s="19">
+      <c r="U40" s="16">
         <v>28.382920012841012</v>
       </c>
-      <c r="U40" s="19">
+      <c r="V40" s="16">
         <v>25.202839310007185</v>
       </c>
-      <c r="V40" s="19">
+      <c r="W40" s="16">
         <v>25.752034916275505</v>
       </c>
-      <c r="W40" s="19">
+      <c r="X40" s="16">
         <v>28.387401545938712</v>
       </c>
-      <c r="X40" s="19">
+      <c r="Y40" s="16">
         <v>26.63684934705848</v>
       </c>
-      <c r="Y40" s="19">
-        <v>25.773441154864766</v>
-      </c>
-      <c r="Z40" s="19">
-        <v>26.635138967231935</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z40" s="16">
+        <v>25.736980658351577</v>
+      </c>
+      <c r="AA40" s="16">
+        <v>26.55033581707476</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
       <c r="F41" s="16"/>
       <c r="G41" s="16"/>
       <c r="H41" s="16"/>
       <c r="I41" s="16"/>
       <c r="J41" s="16"/>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="16"/>
+      <c r="N41" s="16"/>
+      <c r="O41" s="16"/>
+      <c r="P41" s="16"/>
+      <c r="Q41" s="16"/>
+      <c r="R41" s="16"/>
+      <c r="S41" s="16"/>
+      <c r="T41" s="16"/>
+      <c r="U41" s="16"/>
+      <c r="V41" s="16"/>
+      <c r="W41" s="16"/>
+      <c r="X41" s="16"/>
+      <c r="Y41" s="16"/>
+      <c r="Z41" s="16"/>
+      <c r="AA41" s="16"/>
+    </row>
+    <row r="42" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="20">
+        <v>1545916.7920298965</v>
+      </c>
+      <c r="C42" s="15">
         <v>1760468.7734881092</v>
       </c>
-      <c r="C42" s="18">
+      <c r="D42" s="15">
         <v>1907247.2996567565</v>
       </c>
-      <c r="D42" s="18">
+      <c r="E42" s="15">
         <v>2135734.4623516006</v>
       </c>
-      <c r="E42" s="18">
+      <c r="F42" s="15">
         <v>2411645.7434300976</v>
       </c>
-      <c r="F42" s="18">
+      <c r="G42" s="15">
         <v>2521687.4484289587</v>
       </c>
-      <c r="G42" s="18">
+      <c r="H42" s="15">
         <v>2594297.8921789494</v>
       </c>
-      <c r="H42" s="18">
+      <c r="I42" s="15">
         <v>2564791.782658454</v>
       </c>
-      <c r="I42" s="18">
+      <c r="J42" s="15">
         <v>2763169.9826350166</v>
       </c>
-      <c r="J42" s="18">
+      <c r="K42" s="15">
         <v>2573096.0174895045</v>
       </c>
-      <c r="K42" s="18">
+      <c r="L42" s="15">
         <v>3123385.6765948157</v>
       </c>
-      <c r="L42" s="18">
+      <c r="M42" s="15">
         <v>3214884.5465732133</v>
       </c>
-      <c r="M42" s="18">
+      <c r="N42" s="15">
         <v>3359646.2979975445</v>
       </c>
-      <c r="N42" s="18">
+      <c r="O42" s="15">
         <v>3572682.5591714513</v>
       </c>
-      <c r="O42" s="18">
+      <c r="P42" s="15">
         <v>3977060.3993742228</v>
       </c>
-      <c r="P42" s="18">
+      <c r="Q42" s="15">
         <v>4452862.3803569088</v>
       </c>
-      <c r="Q42" s="18">
+      <c r="R42" s="15">
         <v>5311929.3134412505</v>
       </c>
-      <c r="R42" s="18">
+      <c r="S42" s="15">
         <v>6393529.4434898216</v>
       </c>
-      <c r="S42" s="18">
+      <c r="T42" s="15">
         <v>7662209.4908494633</v>
       </c>
-      <c r="T42" s="18">
+      <c r="U42" s="15">
         <v>7896717.0848549977</v>
       </c>
-      <c r="U42" s="18">
+      <c r="V42" s="15">
         <v>5918045.172462482</v>
       </c>
-      <c r="V42" s="18">
+      <c r="W42" s="15">
         <v>7324124.6490688473</v>
       </c>
-      <c r="W42" s="18">
+      <c r="X42" s="15">
         <v>9701755.5986976214</v>
       </c>
-      <c r="X42" s="18">
+      <c r="Y42" s="15">
         <v>9915829.6467580777</v>
       </c>
-      <c r="Y42" s="18">
-        <v>10608176.029042769</v>
-      </c>
-      <c r="Z42" s="18">
-        <v>11211082.460867602</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z42" s="15">
+        <v>10613317.150673412</v>
+      </c>
+      <c r="AA42" s="15">
+        <v>11272113.549099298</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="18">
+      <c r="B43" s="20">
+        <v>34921.771807622914</v>
+      </c>
+      <c r="C43" s="15">
         <v>34558.418823138556</v>
       </c>
-      <c r="C43" s="18">
+      <c r="D43" s="15">
         <v>36901.707804351012</v>
       </c>
-      <c r="D43" s="18">
+      <c r="E43" s="15">
         <v>39403.402026390104</v>
       </c>
-      <c r="E43" s="18">
+      <c r="F43" s="15">
         <v>43031.106157249211</v>
       </c>
-      <c r="F43" s="18">
+      <c r="G43" s="15">
         <v>45773.549023684631</v>
       </c>
-      <c r="G43" s="18">
+      <c r="H43" s="15">
         <v>50576.537717930216</v>
       </c>
-      <c r="H43" s="18">
+      <c r="I43" s="15">
         <v>55766.893983942362</v>
       </c>
-      <c r="I43" s="18">
+      <c r="J43" s="15">
         <v>62288.447088510729</v>
       </c>
-      <c r="J43" s="18">
+      <c r="K43" s="15">
         <v>54035.515943543971</v>
       </c>
-      <c r="K43" s="18">
+      <c r="L43" s="15">
         <v>69304.347672008109</v>
       </c>
-      <c r="L43" s="18">
+      <c r="M43" s="15">
         <v>74217.379596468658</v>
       </c>
-      <c r="M43" s="18">
+      <c r="N43" s="15">
         <v>79593.585553551369</v>
       </c>
-      <c r="N43" s="18">
+      <c r="O43" s="15">
         <v>84600.85750088343</v>
       </c>
-      <c r="O43" s="18">
+      <c r="P43" s="15">
         <v>89624.681701031397</v>
       </c>
-      <c r="P43" s="18">
+      <c r="Q43" s="15">
         <v>97809.150231671243</v>
       </c>
-      <c r="Q43" s="18">
+      <c r="R43" s="15">
         <v>111859.6128950999</v>
       </c>
-      <c r="R43" s="18">
+      <c r="S43" s="15">
         <v>126845.23051852969</v>
       </c>
-      <c r="S43" s="18">
+      <c r="T43" s="15">
         <v>145458.59861232564</v>
       </c>
-      <c r="T43" s="18">
+      <c r="U43" s="15">
         <v>152496.67669719702</v>
       </c>
-      <c r="U43" s="18">
+      <c r="V43" s="15">
         <v>119315.2253912283</v>
       </c>
-      <c r="V43" s="18">
+      <c r="W43" s="15">
         <v>148558.75441913962</v>
       </c>
-      <c r="W43" s="18">
+      <c r="X43" s="15">
         <v>178116.60741224373</v>
       </c>
-      <c r="X43" s="18">
+      <c r="Y43" s="15">
         <v>178258.05802405308</v>
       </c>
-      <c r="Y43" s="18">
-        <v>185161.1211680992</v>
-      </c>
-      <c r="Z43" s="18">
-        <v>195035.53886749747</v>
-      </c>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z43" s="15">
+        <v>185250.85292395129</v>
+      </c>
+      <c r="AA43" s="15">
+        <v>196092.40891804255</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B44" s="19">
+      <c r="B44" s="22">
+        <v>41.809149236926764</v>
+      </c>
+      <c r="C44" s="16">
         <v>43.744887116177992</v>
       </c>
-      <c r="C44" s="19">
+      <c r="D44" s="16">
         <v>43.839124148414157</v>
       </c>
-      <c r="D44" s="19">
+      <c r="E44" s="16">
         <v>45.269625991508633</v>
       </c>
-      <c r="E44" s="19">
+      <c r="F44" s="16">
         <v>45.298443832970037</v>
       </c>
-      <c r="F44" s="19">
+      <c r="G44" s="16">
         <v>42.615635355627049</v>
       </c>
-      <c r="G44" s="19">
+      <c r="H44" s="16">
         <v>39.605079301908894</v>
       </c>
-      <c r="H44" s="19">
+      <c r="I44" s="16">
         <v>35.630793653854155</v>
       </c>
-      <c r="I44" s="19">
+      <c r="J44" s="16">
         <v>34.324237529869976</v>
       </c>
-      <c r="J44" s="19">
+      <c r="K44" s="16">
         <v>30.667065187368824</v>
       </c>
-      <c r="K44" s="19">
+      <c r="L44" s="16">
         <v>33.229448794248945</v>
       </c>
-      <c r="L44" s="19">
+      <c r="M44" s="16">
         <v>31.690407821560047</v>
       </c>
-      <c r="M44" s="19">
+      <c r="N44" s="16">
         <v>30.374931655651977</v>
       </c>
-      <c r="N44" s="19">
+      <c r="O44" s="16">
         <v>29.647361422889258</v>
       </c>
-      <c r="O44" s="19">
+      <c r="P44" s="16">
         <v>30.113667896489204</v>
       </c>
-      <c r="P44" s="19">
+      <c r="Q44" s="16">
         <v>31.933534866036172</v>
       </c>
-      <c r="Q44" s="19">
+      <c r="R44" s="16">
         <v>35.103062422205809</v>
       </c>
-      <c r="R44" s="19">
+      <c r="S44" s="16">
         <v>38.616078887881741</v>
       </c>
-      <c r="S44" s="19">
+      <c r="T44" s="16">
         <v>41.949792926058507</v>
       </c>
-      <c r="T44" s="19">
+      <c r="U44" s="16">
         <v>40.458922246735227</v>
       </c>
-      <c r="U44" s="19">
+      <c r="V44" s="16">
         <v>32.966720991792627</v>
       </c>
-      <c r="V44" s="19">
+      <c r="W44" s="16">
         <v>37.732574897524614</v>
       </c>
-      <c r="W44" s="19">
+      <c r="X44" s="16">
         <v>44.042282065042649</v>
       </c>
-      <c r="X44" s="19">
+      <c r="Y44" s="16">
         <v>40.783119970102177</v>
       </c>
-      <c r="Y44" s="19">
-        <v>40.112031373924289</v>
-      </c>
-      <c r="Z44" s="19">
-        <v>40.019192675133588</v>
-      </c>
-    </row>
-    <row r="45" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="Z44" s="16">
+        <v>40.126807729923549</v>
+      </c>
+      <c r="AA44" s="16">
+        <v>40.24326951435949</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B45" s="19">
+      <c r="B45" s="23">
+        <v>83.388161610660063</v>
+      </c>
+      <c r="C45" s="16">
         <v>81.451798624493094</v>
       </c>
-      <c r="C45" s="19">
+      <c r="D45" s="16">
         <v>81.410502940653515</v>
       </c>
-      <c r="D45" s="19">
+      <c r="E45" s="16">
         <v>81.425472783118664</v>
       </c>
-      <c r="E45" s="19">
+      <c r="F45" s="16">
         <v>80.032973808895662</v>
       </c>
-      <c r="F45" s="19">
+      <c r="G45" s="16">
         <v>79.931050920215696</v>
       </c>
-      <c r="G45" s="19">
+      <c r="H45" s="16">
         <v>77.336194552381755</v>
       </c>
-      <c r="H45" s="19">
+      <c r="I45" s="16">
         <v>75.648634843516774</v>
       </c>
-      <c r="I45" s="19">
+      <c r="J45" s="16">
         <v>72.506656083607922</v>
       </c>
-      <c r="J45" s="19">
+      <c r="K45" s="16">
         <v>76.526709075198625</v>
       </c>
-      <c r="K45" s="19">
+      <c r="L45" s="16">
         <v>75.328088192322227</v>
       </c>
-      <c r="L45" s="19">
+      <c r="M45" s="16">
         <v>69.047364484521168</v>
       </c>
-      <c r="M45" s="19">
+      <c r="N45" s="16">
         <v>70.101929284528467</v>
       </c>
-      <c r="N45" s="19">
+      <c r="O45" s="16">
         <v>66.681233184250132</v>
       </c>
-      <c r="O45" s="19">
+      <c r="P45" s="16">
         <v>69.421740516003055</v>
       </c>
-      <c r="P45" s="19">
+      <c r="Q45" s="16">
         <v>70.57912490692442</v>
       </c>
-      <c r="Q45" s="19">
+      <c r="R45" s="16">
         <v>69.216295695629952</v>
       </c>
-      <c r="R45" s="19">
+      <c r="S45" s="16">
         <v>67.922032437298697</v>
       </c>
-      <c r="S45" s="19">
+      <c r="T45" s="16">
         <v>69.871059529863984</v>
       </c>
-      <c r="T45" s="19">
+      <c r="U45" s="16">
         <v>68.7775892606154</v>
       </c>
-      <c r="U45" s="19">
+      <c r="V45" s="16">
         <v>68.893657237613425</v>
       </c>
-      <c r="V45" s="19">
+      <c r="W45" s="16">
         <v>68.597515069831175</v>
       </c>
-      <c r="W45" s="19">
+      <c r="X45" s="16">
         <v>71.784281152146065</v>
       </c>
-      <c r="X45" s="19">
-        <v>71.866323848529376</v>
-      </c>
-      <c r="Y45" s="19">
-        <v>68.25689514322201</v>
-      </c>
-      <c r="Z45" s="19">
-        <v>71.941820755228875</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="Y45" s="16">
+        <v>71.802008365277359</v>
+      </c>
+      <c r="Z45" s="16">
+        <v>68.24103153828348</v>
+      </c>
+      <c r="AA45" s="16">
+        <v>71.606883821464535</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B46" s="19">
+      <c r="B46" s="22">
+        <v>58.121811261345542</v>
+      </c>
+      <c r="C46" s="16">
         <v>58.362276310601267</v>
       </c>
-      <c r="C46" s="19">
+      <c r="D46" s="16">
         <v>59.02923147155353</v>
       </c>
-      <c r="D46" s="19">
+      <c r="E46" s="16">
         <v>59.268229757853987</v>
       </c>
-      <c r="E46" s="19">
+      <c r="F46" s="16">
         <v>60.510560286470138</v>
       </c>
-      <c r="F46" s="19">
+      <c r="G46" s="16">
         <v>61.474041059006865</v>
       </c>
-      <c r="G46" s="19">
+      <c r="H46" s="16">
         <v>62.811315235311838</v>
       </c>
-      <c r="H46" s="19">
+      <c r="I46" s="16">
         <v>61.961772507129176</v>
       </c>
-      <c r="I46" s="19">
+      <c r="J46" s="16">
         <v>62.710640382742596</v>
       </c>
-      <c r="J46" s="19">
+      <c r="K46" s="16">
         <v>60.698105531525897</v>
       </c>
-      <c r="K46" s="19">
+      <c r="L46" s="16">
         <v>62.176574982718122</v>
       </c>
-      <c r="L46" s="19">
+      <c r="M46" s="16">
         <v>61.529175947158187</v>
       </c>
-      <c r="M46" s="19">
+      <c r="N46" s="16">
         <v>63.336592242972699</v>
       </c>
-      <c r="N46" s="19">
+      <c r="O46" s="16">
         <v>64.181044354974873</v>
       </c>
-      <c r="O46" s="19">
+      <c r="P46" s="16">
         <v>63.272413683934566</v>
       </c>
-      <c r="P46" s="19">
+      <c r="Q46" s="16">
         <v>60.302948643997766</v>
       </c>
-      <c r="Q46" s="19">
+      <c r="R46" s="16">
         <v>58.215197740300965</v>
       </c>
-      <c r="R46" s="19">
+      <c r="S46" s="16">
         <v>57.451388237169219</v>
       </c>
-      <c r="S46" s="19">
+      <c r="T46" s="16">
         <v>58.829659854622456</v>
       </c>
-      <c r="T46" s="19">
+      <c r="U46" s="16">
         <v>59.400392938071938</v>
       </c>
-      <c r="U46" s="19">
+      <c r="V46" s="16">
         <v>57.000545613373056</v>
       </c>
-      <c r="V46" s="19">
+      <c r="W46" s="16">
         <v>58.570680924836843</v>
       </c>
-      <c r="W46" s="19">
+      <c r="X46" s="16">
         <v>63.350970940984077</v>
       </c>
-      <c r="X46" s="19">
-        <v>62.686398373811549</v>
-      </c>
-      <c r="Y46" s="19">
-        <v>60.864942674198815</v>
-      </c>
-      <c r="Z46" s="19">
-        <v>61.120819461796977</v>
-      </c>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y46" s="16">
+        <v>62.686438864429142</v>
+      </c>
+      <c r="Z46" s="16">
+        <v>60.880156079146431</v>
+      </c>
+      <c r="AA46" s="16">
+        <v>61.056780965632839</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B47" s="19">
+      <c r="B47" s="22">
+        <v>8.615601995762951</v>
+      </c>
+      <c r="C47" s="16">
         <v>8.7388754059106635</v>
       </c>
-      <c r="C47" s="19">
+      <c r="D47" s="16">
         <v>8.7038339885836038</v>
       </c>
-      <c r="D47" s="19">
+      <c r="E47" s="16">
         <v>8.601575699411848</v>
       </c>
-      <c r="E47" s="19">
+      <c r="F47" s="16">
         <v>8.5320599379269879</v>
       </c>
-      <c r="F47" s="19">
+      <c r="G47" s="16">
         <v>8.8919330234352856</v>
       </c>
-      <c r="G47" s="19">
+      <c r="H47" s="16">
         <v>8.4230406917483069</v>
       </c>
-      <c r="H47" s="19">
+      <c r="I47" s="16">
         <v>8.2410292163636161</v>
       </c>
-      <c r="I47" s="19">
+      <c r="J47" s="16">
         <v>8.5654264264098465</v>
       </c>
-      <c r="J47" s="19">
+      <c r="K47" s="16">
         <v>10.352934973344945</v>
       </c>
-      <c r="K47" s="19">
+      <c r="L47" s="16">
         <v>10.087944230702121</v>
       </c>
-      <c r="L47" s="19">
+      <c r="M47" s="16">
         <v>9.7414505282985697</v>
       </c>
-      <c r="M47" s="19">
+      <c r="N47" s="16">
         <v>9.9383904560367213</v>
       </c>
-      <c r="N47" s="19">
+      <c r="O47" s="16">
         <v>10.522044026595275</v>
       </c>
-      <c r="O47" s="19">
+      <c r="P47" s="16">
         <v>10.333414314097805</v>
       </c>
-      <c r="P47" s="19">
+      <c r="Q47" s="16">
         <v>10.256034242795208</v>
       </c>
-      <c r="Q47" s="19">
+      <c r="R47" s="16">
         <v>9.995595148719925</v>
       </c>
-      <c r="R47" s="19">
+      <c r="S47" s="16">
         <v>9.9358659029395682</v>
       </c>
-      <c r="S47" s="19">
+      <c r="T47" s="16">
         <v>9.6335100194600773</v>
       </c>
-      <c r="T47" s="19">
+      <c r="U47" s="16">
         <v>9.1011162832548731</v>
       </c>
-      <c r="U47" s="19">
+      <c r="V47" s="16">
         <v>7.0444640849358446</v>
       </c>
-      <c r="V47" s="19">
+      <c r="W47" s="16">
         <v>3.43459296539839</v>
       </c>
-      <c r="W47" s="19">
+      <c r="X47" s="16">
         <v>5.5498771938500333</v>
       </c>
-      <c r="X47" s="19">
+      <c r="Y47" s="16">
         <v>9.8768427964064571</v>
       </c>
-      <c r="Y47" s="19">
-        <v>11.527940954855797</v>
-      </c>
-      <c r="Z47" s="19">
-        <v>12.995682033828485</v>
-      </c>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z47" s="16">
+        <v>11.48887825907341</v>
+      </c>
+      <c r="AA47" s="16">
+        <v>13.009475684663174</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
       <c r="F48" s="16"/>
       <c r="G48" s="16"/>
       <c r="H48" s="16"/>
       <c r="I48" s="16"/>
       <c r="J48" s="16"/>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="16"/>
+      <c r="Q48" s="16"/>
+      <c r="R48" s="16"/>
+      <c r="S48" s="16"/>
+      <c r="T48" s="16"/>
+      <c r="U48" s="16"/>
+      <c r="V48" s="16"/>
+      <c r="W48" s="16"/>
+      <c r="X48" s="16"/>
+      <c r="Y48" s="16"/>
+      <c r="Z48" s="16"/>
+      <c r="AA48" s="16"/>
+    </row>
+    <row r="49" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="18">
+      <c r="B49" s="20">
+        <v>434846.85697182402</v>
+      </c>
+      <c r="C49" s="15">
         <v>519114.370034691</v>
       </c>
-      <c r="C49" s="18">
+      <c r="D49" s="15">
         <v>584827.27379791101</v>
       </c>
-      <c r="D49" s="18">
+      <c r="E49" s="15">
         <v>610955.97781578603</v>
       </c>
-      <c r="E49" s="18">
+      <c r="F49" s="15">
         <v>673496.58503984602</v>
       </c>
-      <c r="F49" s="18">
+      <c r="G49" s="15">
         <v>768737.91490434599</v>
       </c>
-      <c r="G49" s="18">
+      <c r="H49" s="15">
         <v>825831.00609565899</v>
       </c>
-      <c r="H49" s="18">
+      <c r="I49" s="15">
         <v>848995.06231564702</v>
       </c>
-      <c r="I49" s="18">
+      <c r="J49" s="15">
         <v>949362.88124150306</v>
       </c>
-      <c r="J49" s="18">
+      <c r="K49" s="15">
         <v>1209347.4708672301</v>
       </c>
-      <c r="K49" s="18">
+      <c r="L49" s="15">
         <v>1286821.7286340899</v>
       </c>
-      <c r="L49" s="18">
+      <c r="M49" s="15">
         <v>1331057.8003026999</v>
       </c>
-      <c r="M49" s="18">
+      <c r="N49" s="15">
         <v>1518865.5738758901</v>
       </c>
-      <c r="N49" s="18">
+      <c r="O49" s="15">
         <v>1707937.4381440801</v>
       </c>
-      <c r="O49" s="18">
+      <c r="P49" s="15">
         <v>1855467.9807921499</v>
       </c>
-      <c r="P49" s="18">
+      <c r="Q49" s="15">
         <v>1914104.6717427899</v>
       </c>
-      <c r="Q49" s="18">
+      <c r="R49" s="15">
         <v>1983722.3506102101</v>
       </c>
-      <c r="R49" s="18">
+      <c r="S49" s="15">
         <v>2143019.3529818701</v>
       </c>
-      <c r="S49" s="18">
+      <c r="T49" s="15">
         <v>2326517.7192999991</v>
       </c>
-      <c r="T49" s="18">
+      <c r="U49" s="15">
         <v>2430628.4430767801</v>
       </c>
-      <c r="U49" s="18">
+      <c r="V49" s="15">
         <v>1740559.0291181721</v>
       </c>
-      <c r="V49" s="18">
+      <c r="W49" s="15">
         <v>941740.52341519285</v>
       </c>
-      <c r="W49" s="18">
+      <c r="X49" s="15">
         <v>1469235.1306790612</v>
       </c>
-      <c r="X49" s="18">
+      <c r="Y49" s="15">
         <v>2879901.4275458022</v>
       </c>
-      <c r="Y49" s="18">
-        <v>3659967.0427601235</v>
-      </c>
-      <c r="Z49" s="18">
-        <v>4379637.3553943578</v>
-      </c>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z49" s="15">
+        <v>3647744.8778076004</v>
+      </c>
+      <c r="AA49" s="15">
+        <v>4393914.288374369</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B50" s="18">
+      <c r="B50" s="20">
+        <v>9844.0526484250859</v>
+      </c>
+      <c r="C50" s="15">
         <v>10185.358291835008</v>
       </c>
-      <c r="C50" s="18">
+      <c r="D50" s="15">
         <v>11319.184607706335</v>
       </c>
-      <c r="D50" s="18">
+      <c r="E50" s="15">
         <v>11275.022372959465</v>
       </c>
-      <c r="E50" s="18">
+      <c r="F50" s="15">
         <v>12018.095396505209</v>
       </c>
-      <c r="F50" s="18">
+      <c r="G50" s="15">
         <v>13953.447833316202</v>
       </c>
-      <c r="G50" s="18">
+      <c r="H50" s="15">
         <v>16101.104241452662</v>
       </c>
-      <c r="H50" s="18">
+      <c r="I50" s="15">
         <v>18417.40400446194</v>
       </c>
-      <c r="I50" s="18">
+      <c r="J50" s="15">
         <v>21300.594414696916</v>
       </c>
-      <c r="J50" s="18">
+      <c r="K50" s="15">
         <v>25391.937998753547</v>
       </c>
-      <c r="K50" s="18">
+      <c r="L50" s="15">
         <v>28528.10963972575</v>
       </c>
-      <c r="L50" s="18">
+      <c r="M50" s="15">
         <v>30733.781968413827</v>
       </c>
-      <c r="M50" s="18">
+      <c r="N50" s="15">
         <v>35998.678071889371</v>
       </c>
-      <c r="N50" s="18">
+      <c r="O50" s="15">
         <v>40447.957283942902</v>
       </c>
-      <c r="O50" s="18">
+      <c r="P50" s="15">
         <v>41805.578945065456</v>
       </c>
-      <c r="P50" s="18">
+      <c r="Q50" s="15">
         <v>42075.923367428593</v>
       </c>
-      <c r="Q50" s="18">
+      <c r="R50" s="15">
         <v>41772.640679501965</v>
       </c>
-      <c r="R50" s="18">
+      <c r="S50" s="15">
         <v>42518.591396345575</v>
       </c>
-      <c r="S50" s="18">
+      <c r="T50" s="15">
         <v>44181.67556706335</v>
       </c>
-      <c r="T50" s="18">
+      <c r="U50" s="15">
         <v>46947.177748612958</v>
       </c>
-      <c r="U50" s="18">
+      <c r="V50" s="15">
         <v>34915.424181576789</v>
       </c>
-      <c r="V50" s="18">
+      <c r="W50" s="15">
         <v>19073.338212022518</v>
       </c>
-      <c r="W50" s="18">
+      <c r="X50" s="15">
         <v>26887.904325572475</v>
       </c>
-      <c r="X50" s="18">
+      <c r="Y50" s="15">
         <v>51709.915317827734</v>
       </c>
-      <c r="Y50" s="18">
-        <v>63851.08111834828</v>
-      </c>
-      <c r="Z50" s="18">
-        <v>76161.661847930576</v>
-      </c>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z50" s="15">
+        <v>63642.953925069596</v>
+      </c>
+      <c r="AA50" s="15">
+        <v>76410.874487768189</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B51" s="19">
+      <c r="B51" s="21"/>
+      <c r="C51" s="16">
         <v>19.378664399160456</v>
       </c>
-      <c r="C51" s="19">
+      <c r="D51" s="16">
         <v>12.658656272379545</v>
       </c>
-      <c r="D51" s="19">
+      <c r="E51" s="16">
         <v>4.467764276483436</v>
       </c>
-      <c r="E51" s="19">
+      <c r="F51" s="16">
         <v>10.236516131268147</v>
       </c>
-      <c r="F51" s="19">
+      <c r="G51" s="16">
         <v>14.141323353386454</v>
       </c>
-      <c r="G51" s="19">
+      <c r="H51" s="16">
         <v>7.4268603231853092</v>
       </c>
-      <c r="H51" s="19">
+      <c r="I51" s="16">
         <v>2.8049390309892175</v>
       </c>
-      <c r="I51" s="19">
+      <c r="J51" s="16">
         <v>11.821955554382299</v>
       </c>
-      <c r="J51" s="19">
+      <c r="K51" s="16">
         <v>27.385164805025795</v>
       </c>
-      <c r="K51" s="19">
+      <c r="L51" s="16">
         <v>6.4062860040797602</v>
       </c>
-      <c r="L51" s="19">
+      <c r="M51" s="16">
         <v>3.4376223749007551</v>
       </c>
-      <c r="M51" s="19">
+      <c r="N51" s="16">
         <v>14.109663271608525</v>
       </c>
-      <c r="N51" s="19">
+      <c r="O51" s="16">
         <v>12.448228962469017</v>
       </c>
-      <c r="O51" s="19">
+      <c r="P51" s="16">
         <v>8.6379359895279748</v>
       </c>
-      <c r="P51" s="19">
+      <c r="Q51" s="16">
         <v>3.1602103381814288</v>
       </c>
-      <c r="Q51" s="19">
+      <c r="R51" s="16">
         <v>3.6370883941280567</v>
       </c>
-      <c r="R51" s="19">
+      <c r="S51" s="16">
         <v>8.0302065620553549</v>
       </c>
-      <c r="S51" s="19">
+      <c r="T51" s="16">
         <v>8.5626089219774428</v>
       </c>
-      <c r="T51" s="19">
+      <c r="U51" s="16">
         <v>4.474959417377903</v>
       </c>
-      <c r="U51" s="19">
+      <c r="V51" s="16">
         <v>-28.390575940314946</v>
       </c>
-      <c r="V51" s="19">
+      <c r="W51" s="16">
         <v>-45.89436453112932</v>
       </c>
-      <c r="W51" s="19">
+      <c r="X51" s="16">
         <v>56.012733247468788</v>
       </c>
-      <c r="X51" s="19">
+      <c r="Y51" s="16">
         <v>96.013651417030133</v>
       </c>
-      <c r="Y51" s="19">
-        <v>27.086538718065725</v>
-      </c>
-      <c r="Z51" s="19">
-        <v>19.663300358341559</v>
-      </c>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z51" s="16">
+        <v>26.662143464963648</v>
+      </c>
+      <c r="AA51" s="16">
+        <v>20.455635894559549</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B52" s="19">
+      <c r="B52" s="21"/>
+      <c r="C52" s="16">
         <v>3.4671253354636065</v>
       </c>
-      <c r="C52" s="19">
+      <c r="D52" s="16">
         <v>11.131923722116355</v>
       </c>
-      <c r="D52" s="19">
+      <c r="E52" s="16">
         <v>-0.3901538518666996</v>
       </c>
-      <c r="E52" s="19">
+      <c r="F52" s="16">
         <v>6.5904350250145001</v>
       </c>
-      <c r="F52" s="19">
+      <c r="G52" s="16">
         <v>16.103653473858955</v>
       </c>
-      <c r="G52" s="19">
+      <c r="H52" s="16">
         <v>15.391582308485567</v>
       </c>
-      <c r="H52" s="19">
+      <c r="I52" s="16">
         <v>14.385968367597485</v>
       </c>
-      <c r="I52" s="19">
+      <c r="J52" s="16">
         <v>15.654705785551926</v>
       </c>
-      <c r="J52" s="19">
+      <c r="K52" s="16">
         <v>19.207649816728576</v>
       </c>
-      <c r="K52" s="19">
+      <c r="L52" s="16">
         <v>12.351052688952507</v>
       </c>
-      <c r="L52" s="19">
+      <c r="M52" s="16">
         <v>7.7315754760583673</v>
       </c>
-      <c r="M52" s="19">
+      <c r="N52" s="16">
         <v>17.130648316847115</v>
       </c>
-      <c r="N52" s="19">
+      <c r="O52" s="16">
         <v>12.359562768300322</v>
       </c>
-      <c r="O52" s="19">
+      <c r="P52" s="16">
         <v>3.3564653255345149</v>
       </c>
-      <c r="P52" s="19">
+      <c r="Q52" s="16">
         <v>0.64667068172499853</v>
       </c>
-      <c r="Q52" s="19">
+      <c r="R52" s="16">
         <v>-0.72079865075855309</v>
       </c>
-      <c r="R52" s="19">
+      <c r="S52" s="16">
         <v>1.785739911840551</v>
       </c>
-      <c r="S52" s="19">
+      <c r="T52" s="16">
         <v>3.9114281919995904</v>
       </c>
-      <c r="T52" s="19">
+      <c r="U52" s="16">
         <v>6.2593872822950232</v>
       </c>
-      <c r="U52" s="19">
+      <c r="V52" s="16">
         <v>-25.628278725213988</v>
       </c>
-      <c r="V52" s="19">
+      <c r="W52" s="16">
         <v>-45.372743825674</v>
       </c>
-      <c r="W52" s="19">
+      <c r="X52" s="16">
         <v>40.971150548907019</v>
       </c>
-      <c r="X52" s="19">
+      <c r="Y52" s="16">
         <v>92.316644286210163</v>
       </c>
-      <c r="Y52" s="19">
-        <v>23.479376684136071</v>
-      </c>
-      <c r="Z52" s="19">
-        <v>19.280144539392481</v>
-      </c>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z52" s="16">
+        <v>23.076886770935729</v>
+      </c>
+      <c r="AA52" s="16">
+        <v>20.06179753650494</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B53" s="19">
+      <c r="B53" s="21">
+        <v>10.747157322584982</v>
+      </c>
+      <c r="C53" s="16">
         <v>11.771934618428585</v>
       </c>
-      <c r="C53" s="19">
+      <c r="D53" s="16">
         <v>12.272555871694047</v>
       </c>
-      <c r="D53" s="19">
+      <c r="E53" s="16">
         <v>11.836090522912359</v>
       </c>
-      <c r="E53" s="19">
+      <c r="F53" s="16">
         <v>11.571084531584166</v>
       </c>
-      <c r="F53" s="19">
+      <c r="G53" s="16">
         <v>11.83621498414924</v>
       </c>
-      <c r="G53" s="19">
+      <c r="H53" s="16">
         <v>11.545385757422098</v>
       </c>
-      <c r="H53" s="19">
+      <c r="I53" s="16">
         <v>10.822487194189819</v>
       </c>
-      <c r="I53" s="19">
+      <c r="J53" s="16">
         <v>10.782910178800128</v>
       </c>
-      <c r="J53" s="19">
+      <c r="K53" s="16">
         <v>12.921216404407293</v>
       </c>
-      <c r="K53" s="19">
+      <c r="L53" s="16">
         <v>12.309313598000205</v>
       </c>
-      <c r="L53" s="19">
+      <c r="M53" s="16">
         <v>11.842617752171734</v>
       </c>
-      <c r="M53" s="19">
+      <c r="N53" s="16">
         <v>12.367467985622604</v>
       </c>
-      <c r="N53" s="19">
+      <c r="O53" s="16">
         <v>12.681762945354839</v>
       </c>
-      <c r="O53" s="19">
+      <c r="P53" s="16">
         <v>12.597534814298273</v>
       </c>
-      <c r="P53" s="19">
+      <c r="Q53" s="16">
         <v>12.319090971260366</v>
       </c>
-      <c r="Q53" s="19">
+      <c r="R53" s="16">
         <v>11.798787250293209</v>
       </c>
-      <c r="R53" s="19">
+      <c r="S53" s="16">
         <v>11.657501351532343</v>
       </c>
-      <c r="S53" s="19">
+      <c r="T53" s="16">
         <v>11.510377784142007</v>
       </c>
-      <c r="T53" s="19">
+      <c r="U53" s="16">
         <v>11.319959068388586</v>
       </c>
-      <c r="U53" s="19">
+      <c r="V53" s="16">
         <v>9.0128364910446557</v>
       </c>
-      <c r="V53" s="19">
+      <c r="W53" s="16">
         <v>4.6850426620599288</v>
       </c>
-      <c r="W53" s="19">
+      <c r="X53" s="16">
         <v>6.2996049439659281</v>
       </c>
-      <c r="X53" s="19">
+      <c r="Y53" s="16">
         <v>10.674939210088704</v>
       </c>
-      <c r="Y53" s="19">
-        <v>12.243828793712911</v>
-      </c>
-      <c r="Z53" s="19">
-        <v>13.60190491261544</v>
-      </c>
-    </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z53" s="16">
+        <v>12.206910768646781</v>
+      </c>
+      <c r="AA53" s="16">
+        <v>13.646190559962207</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="19">
+      <c r="B54" s="21">
+        <v>11.760385314445788</v>
+      </c>
+      <c r="C54" s="16">
         <v>12.899177684679783</v>
       </c>
-      <c r="C54" s="19">
+      <c r="D54" s="16">
         <v>13.442575310511277</v>
       </c>
-      <c r="D54" s="19">
+      <c r="E54" s="16">
         <v>12.949994065528101</v>
       </c>
-      <c r="E54" s="19">
+      <c r="F54" s="16">
         <v>12.650426503244375</v>
       </c>
-      <c r="F54" s="19">
+      <c r="G54" s="16">
         <v>12.991401724277404</v>
       </c>
-      <c r="G54" s="19">
+      <c r="H54" s="16">
         <v>12.60730411299186</v>
       </c>
-      <c r="H54" s="19">
+      <c r="I54" s="16">
         <v>11.794473174409035</v>
       </c>
-      <c r="I54" s="19">
+      <c r="J54" s="16">
         <v>11.79303381354058</v>
       </c>
-      <c r="J54" s="19">
+      <c r="K54" s="16">
         <v>14.413429375033513</v>
       </c>
-      <c r="K54" s="19">
+      <c r="L54" s="16">
         <v>13.690392787352382</v>
       </c>
-      <c r="L54" s="19">
+      <c r="M54" s="16">
         <v>13.120771186207381</v>
       </c>
-      <c r="M54" s="19">
+      <c r="N54" s="16">
         <v>13.732230689909519</v>
       </c>
-      <c r="N54" s="19">
+      <c r="O54" s="16">
         <v>14.173058388955825</v>
       </c>
-      <c r="O54" s="19">
+      <c r="P54" s="16">
         <v>14.049308020299604</v>
       </c>
-      <c r="P54" s="19">
+      <c r="Q54" s="16">
         <v>13.726929568266119</v>
       </c>
-      <c r="Q54" s="19">
+      <c r="R54" s="16">
         <v>13.109122014404834</v>
       </c>
-      <c r="R54" s="19">
+      <c r="S54" s="16">
         <v>12.943555687738332</v>
       </c>
-      <c r="S54" s="19">
+      <c r="T54" s="16">
         <v>12.737440379305118</v>
       </c>
-      <c r="T54" s="19">
+      <c r="U54" s="16">
         <v>12.45335322671653</v>
       </c>
-      <c r="U54" s="19">
+      <c r="V54" s="16">
         <v>9.6958577047846983</v>
       </c>
-      <c r="V54" s="19">
+      <c r="W54" s="16">
         <v>4.8516780552492991</v>
       </c>
-      <c r="W54" s="19">
+      <c r="X54" s="16">
         <v>6.6697689286177821</v>
       </c>
-      <c r="X54" s="19">
+      <c r="Y54" s="16">
         <v>11.84483493623441</v>
       </c>
-      <c r="Y54" s="19">
-        <v>13.839204067201955</v>
-      </c>
-      <c r="Z54" s="19">
-        <v>15.633597539267017</v>
-      </c>
-    </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z54" s="16">
+        <v>13.791386357498208</v>
+      </c>
+      <c r="AA54" s="16">
+        <v>15.686985068046456</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B55" s="19">
+      <c r="B55" s="21">
+        <v>19.369180579977559</v>
+      </c>
+      <c r="C55" s="16">
         <v>18.311758484272481</v>
       </c>
-      <c r="C55" s="19">
+      <c r="D55" s="16">
         <v>18.343864205566344</v>
       </c>
-      <c r="D55" s="19">
+      <c r="E55" s="16">
         <v>18.628277923141816</v>
       </c>
-      <c r="E55" s="19">
+      <c r="F55" s="16">
         <v>18.544600681754027</v>
       </c>
-      <c r="F55" s="19">
+      <c r="G55" s="16">
         <v>18.181518197190901</v>
       </c>
-      <c r="G55" s="19">
+      <c r="H55" s="16">
         <v>18.71891305527387</v>
       </c>
-      <c r="H55" s="19">
+      <c r="I55" s="16">
         <v>18.873986421652862</v>
       </c>
-      <c r="I55" s="19">
+      <c r="J55" s="16">
         <v>19.083916854465937</v>
       </c>
-      <c r="J55" s="19">
+      <c r="K55" s="16">
         <v>18.615417837598201</v>
       </c>
-      <c r="K55" s="19">
+      <c r="L55" s="16">
         <v>20.402136173609264</v>
       </c>
-      <c r="L55" s="19">
+      <c r="M55" s="16">
         <v>18.966638661776219</v>
       </c>
-      <c r="M55" s="19">
+      <c r="N55" s="16">
         <v>19.930064950674449</v>
       </c>
-      <c r="N55" s="19">
+      <c r="O55" s="16">
         <v>20.783014402777798</v>
       </c>
-      <c r="O55" s="19">
+      <c r="P55" s="16">
         <v>20.862173341111859</v>
       </c>
-      <c r="P55" s="19">
+      <c r="Q55" s="16">
         <v>22.23164338100969</v>
       </c>
-      <c r="Q55" s="19">
+      <c r="R55" s="16">
         <v>24.996623925343183</v>
       </c>
-      <c r="R55" s="19">
+      <c r="S55" s="16">
         <v>25.642928189743618</v>
       </c>
-      <c r="S55" s="19">
+      <c r="T55" s="16">
         <v>27.283299001978968</v>
       </c>
-      <c r="T55" s="19">
+      <c r="U55" s="16">
         <v>27.155125213001142</v>
       </c>
-      <c r="U55" s="19">
+      <c r="V55" s="16">
         <v>21.302262064147431</v>
       </c>
-      <c r="V55" s="19">
+      <c r="W55" s="16">
         <v>22.279279593599281</v>
       </c>
-      <c r="W55" s="19">
+      <c r="X55" s="16">
         <v>23.345966768073843</v>
       </c>
-      <c r="X55" s="19">
+      <c r="Y55" s="16">
         <v>23.634505580337862</v>
       </c>
-      <c r="Y55" s="19">
-        <v>23.570507069845377</v>
-      </c>
-      <c r="Z55" s="19">
-        <v>22.686153371928842</v>
-      </c>
-    </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z55" s="16">
+        <v>23.557863932735653</v>
+      </c>
+      <c r="AA55" s="16">
+        <v>22.736478643720119</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B56" s="19">
+      <c r="B56" s="21">
+        <v>71.717880739706757</v>
+      </c>
+      <c r="C56" s="16">
         <v>72.902463502990926</v>
       </c>
-      <c r="C56" s="19">
+      <c r="D56" s="16">
         <v>73.104271776073261</v>
       </c>
-      <c r="D56" s="19">
+      <c r="E56" s="16">
         <v>73.504658707853338</v>
       </c>
-      <c r="E56" s="19">
+      <c r="F56" s="16">
         <v>73.599671035212452</v>
       </c>
-      <c r="F56" s="19">
+      <c r="G56" s="16">
         <v>73.953880515660273</v>
       </c>
-      <c r="G56" s="19">
+      <c r="H56" s="16">
         <v>73.277386327772675</v>
       </c>
-      <c r="H56" s="19">
+      <c r="I56" s="16">
         <v>72.256377860348692</v>
       </c>
-      <c r="I56" s="19">
+      <c r="J56" s="16">
         <v>73.185824519455394</v>
       </c>
-      <c r="J56" s="19">
+      <c r="K56" s="16">
         <v>73.189219811702145</v>
       </c>
-      <c r="K56" s="19">
+      <c r="L56" s="16">
         <v>70.192452758458145</v>
       </c>
-      <c r="L56" s="19">
+      <c r="M56" s="16">
         <v>72.131410196483074</v>
       </c>
-      <c r="M56" s="19">
+      <c r="N56" s="16">
         <v>72.554982720619748</v>
       </c>
-      <c r="N56" s="19">
+      <c r="O56" s="16">
         <v>72.01076248781429</v>
       </c>
-      <c r="O56" s="19">
+      <c r="P56" s="16">
         <v>71.274020585631362</v>
       </c>
-      <c r="P56" s="19">
+      <c r="Q56" s="16">
         <v>72.472888094123675</v>
       </c>
-      <c r="Q56" s="19">
+      <c r="R56" s="16">
         <v>72.553588372860673</v>
       </c>
-      <c r="R56" s="19">
+      <c r="S56" s="16">
         <v>72.18164786384402</v>
       </c>
-      <c r="S56" s="19">
+      <c r="T56" s="16">
         <v>72.542821859193097</v>
       </c>
-      <c r="T56" s="19">
+      <c r="U56" s="16">
         <v>73.206439338573048</v>
       </c>
-      <c r="U56" s="19">
+      <c r="V56" s="16">
         <v>75.069048066255249</v>
       </c>
-      <c r="V56" s="19">
+      <c r="W56" s="16">
         <v>75.260608124363884</v>
       </c>
-      <c r="W56" s="19">
+      <c r="X56" s="16">
         <v>75.925344622330655</v>
       </c>
-      <c r="X56" s="19">
+      <c r="Y56" s="16">
         <v>76.518844218519618</v>
       </c>
-      <c r="Y56" s="19">
-        <v>76.145393421070068</v>
-      </c>
-      <c r="Z56" s="19">
-        <v>76.419216296468377</v>
-      </c>
-    </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z56" s="16">
+        <v>76.148686816092123</v>
+      </c>
+      <c r="AA56" s="16">
+        <v>76.409190501696543</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B57" s="19">
+      <c r="B57" s="21">
+        <v>25.279565250464366</v>
+      </c>
+      <c r="C57" s="16">
         <v>25.311545894660203</v>
       </c>
-      <c r="C57" s="19">
+      <c r="D57" s="16">
         <v>25.135408677667055</v>
       </c>
-      <c r="D57" s="19">
+      <c r="E57" s="16">
         <v>24.836872645199691</v>
       </c>
-      <c r="E57" s="19">
+      <c r="F57" s="16">
         <v>24.011997883481044</v>
       </c>
-      <c r="F57" s="19">
+      <c r="G57" s="16">
         <v>24.269901165699213</v>
       </c>
-      <c r="G57" s="19">
+      <c r="H57" s="16">
         <v>23.829185395826364</v>
       </c>
-      <c r="H57" s="19">
+      <c r="I57" s="16">
         <v>23.150911599305608</v>
       </c>
-      <c r="I57" s="19">
+      <c r="J57" s="16">
         <v>23.268667677685031</v>
       </c>
-      <c r="J57" s="19">
+      <c r="K57" s="16">
         <v>21.738614391940967</v>
       </c>
-      <c r="K57" s="19">
+      <c r="L57" s="16">
         <v>21.919201716811969</v>
       </c>
-      <c r="L57" s="19">
+      <c r="M57" s="16">
         <v>21.704326952608653</v>
       </c>
-      <c r="M57" s="19">
+      <c r="N57" s="16">
         <v>21.328571209116543</v>
       </c>
-      <c r="N57" s="19">
+      <c r="O57" s="16">
         <v>20.434498765561393</v>
       </c>
-      <c r="O57" s="19">
+      <c r="P57" s="16">
         <v>20.575083990644508</v>
       </c>
-      <c r="P57" s="19">
+      <c r="Q57" s="16">
         <v>19.928022374343051</v>
       </c>
-      <c r="Q57" s="19">
+      <c r="R57" s="16">
         <v>19.590303199427083</v>
       </c>
-      <c r="R57" s="19">
+      <c r="S57" s="16">
         <v>19.500202055522461</v>
       </c>
-      <c r="S57" s="19">
+      <c r="T57" s="16">
         <v>19.098247166991765</v>
       </c>
-      <c r="T57" s="19">
+      <c r="U57" s="16">
         <v>18.516454400330357</v>
       </c>
-      <c r="U57" s="19">
+      <c r="V57" s="16">
         <v>17.6581790476138</v>
       </c>
-      <c r="V57" s="19">
+      <c r="W57" s="16">
         <v>17.640084696340029</v>
       </c>
-      <c r="W57" s="19">
+      <c r="X57" s="16">
         <v>17.229379413025146</v>
       </c>
-      <c r="X57" s="19">
+      <c r="Y57" s="16">
         <v>16.23032629491793</v>
       </c>
-      <c r="Y57" s="19">
-        <v>15.677153099355342</v>
-      </c>
-      <c r="Z57" s="19">
-        <v>15.32570445775093</v>
-      </c>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z57" s="16">
+        <v>15.672233280806077</v>
+      </c>
+      <c r="AA57" s="16">
+        <v>15.330343811665193</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B58" s="19">
+      <c r="B58" s="21">
+        <v>6.1619888202914881</v>
+      </c>
+      <c r="C58" s="17">
         <v>6.8193785973778063</v>
       </c>
-      <c r="C58" s="19">
+      <c r="D58" s="17">
         <v>8.2278837379223724</v>
       </c>
-      <c r="D58" s="19">
+      <c r="E58" s="17">
         <v>9.9620397080273744</v>
       </c>
-      <c r="E58" s="19">
+      <c r="F58" s="17">
         <v>8.4861782812479376</v>
       </c>
-      <c r="F58" s="19">
+      <c r="G58" s="17">
         <v>11.109728529771177</v>
       </c>
-      <c r="G58" s="19">
+      <c r="H58" s="17">
         <v>12.823488726280127</v>
       </c>
-      <c r="H58" s="19">
+      <c r="I58" s="17">
         <v>8.4762328805611258</v>
       </c>
-      <c r="I58" s="19">
+      <c r="J58" s="17">
         <v>7.0062725959761947</v>
       </c>
-      <c r="J58" s="19">
+      <c r="K58" s="17">
         <v>9.288007808208258</v>
       </c>
-      <c r="K58" s="19">
+      <c r="L58" s="17">
         <v>9.9923072546896385</v>
       </c>
-      <c r="L58" s="19">
+      <c r="M58" s="17">
         <v>9.1729922766698415</v>
       </c>
-      <c r="M58" s="19">
+      <c r="N58" s="17">
         <v>5.4178128233454608</v>
       </c>
-      <c r="N58" s="19">
+      <c r="O58" s="17">
         <v>5.7965749808171108</v>
       </c>
-      <c r="O58" s="19">
+      <c r="P58" s="17">
         <v>5.7208815440089174</v>
       </c>
-      <c r="P58" s="19">
+      <c r="Q58" s="17">
         <v>5.7175128937446527</v>
       </c>
-      <c r="Q58" s="19">
+      <c r="R58" s="17">
         <v>5.2203613922703429</v>
       </c>
-      <c r="R58" s="19">
+      <c r="S58" s="17">
         <v>4.1099277660649944</v>
       </c>
-      <c r="S58" s="19">
+      <c r="T58" s="17">
         <v>3.972523635092017</v>
       </c>
-      <c r="T58" s="19">
+      <c r="U58" s="17">
         <v>4.3162972943794804</v>
       </c>
-      <c r="U58" s="19">
+      <c r="V58" s="17">
         <v>5.3614585164152704</v>
       </c>
-      <c r="V58" s="19">
+      <c r="W58" s="17">
         <v>6.2031472566573047</v>
       </c>
-      <c r="W58" s="19">
+      <c r="X58" s="17">
         <v>5.8705501064982091</v>
       </c>
-      <c r="X58" s="19">
-        <v>6.5955408804101179</v>
-      </c>
-      <c r="Y58" s="19">
-        <v>7.6405269932896163</v>
-      </c>
-      <c r="Z58" s="19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="59" spans="1:26" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y58" s="17">
+        <v>6.465276139918597</v>
+      </c>
+      <c r="Z58" s="17">
+        <v>7.6396391320373898</v>
+      </c>
+      <c r="AA58" s="17">
+        <v>7.5086608220468145</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12"/>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
@@ -4052,18 +4289,33 @@
       <c r="X59" s="12"/>
       <c r="Y59" s="12"/>
       <c r="Z59" s="12"/>
-    </row>
-    <row r="60" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA59" s="12"/>
+    </row>
+    <row r="60" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A61" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="B60" s="21"/>
+    </row>
+    <row r="61" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B61" s="24"/>
+    </row>
+    <row r="63" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B63" s="19"/>
+    </row>
+    <row r="64" spans="1:27" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B64" s="19"/>
+    </row>
+    <row r="65" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B65" s="19"/>
+    </row>
+    <row r="66" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B66" s="19"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B7:AA7"/>
+  </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="59" orientation="landscape" r:id="rId1"/>
